--- a/Time to Fixation Experiments - Changing Chemotaxis Equation/Experiment 1 - Testing Fixation Time/Time_for_Bac_Fix_Pos50_Start.xlsx
+++ b/Time to Fixation Experiments - Changing Chemotaxis Equation/Experiment 1 - Testing Fixation Time/Time_for_Bac_Fix_Pos50_Start.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\Time to Fixation Experiments - Changing Chemotaxis Equation\Experiment 1 - Testing Fixation Time\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E8F30A-45B9-4195-9792-CF3D74CAC5FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{431272C5-D09C-482B-A84B-5972162A8044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C5D5DF43-D68A-448F-BEE9-BC751A2734F3}"/>
   </bookViews>
@@ -435,502 +435,502 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>4621</v>
+        <v>4172</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>9307</v>
+        <v>4562</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>1919</v>
+        <v>4322</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>2046</v>
+        <v>7782</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>4033</v>
+        <v>10876</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>11206</v>
+        <v>5951</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>3268</v>
+        <v>12391</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>6429</v>
+        <v>6623</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>6984</v>
+        <v>5401</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>12850</v>
+        <v>6899</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>3891</v>
+        <v>6561</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>3288</v>
+        <v>8902</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>1533</v>
+        <v>4153</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>6961</v>
+        <v>5442</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>9003</v>
+        <v>20536</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>5071</v>
+        <v>8271</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>16124</v>
+        <v>5069</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>10222</v>
+        <v>9490</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>7144</v>
+        <v>10777</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>5012</v>
+        <v>7897</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>3129</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>4995</v>
+        <v>16702</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>6899</v>
+        <v>4945</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>14015</v>
+        <v>6493</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>1687</v>
+        <v>3877</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>6132</v>
+        <v>3922</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>5460</v>
+        <v>15518</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>5177</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>9816</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>9525</v>
+        <v>4528</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>8508</v>
+        <v>14678</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>11641</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>5647</v>
+        <v>3380</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>18367</v>
+        <v>15302</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>10715</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>3351</v>
+        <v>13442</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>3079</v>
+        <v>3958</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>6130</v>
+        <v>6599</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>14350</v>
+        <v>8944</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>2793</v>
+        <v>9477</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>3014</v>
+        <v>4359</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>5409</v>
+        <v>5767</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>2491</v>
+        <v>8001</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>1764</v>
+        <v>23108</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>44481</v>
+        <v>8586</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>6197</v>
+        <v>3283</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>2970</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>6317</v>
+        <v>6199</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>6136</v>
+        <v>9403</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>2815</v>
+        <v>18052</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>8107</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>5353</v>
+        <v>3237</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>1557</v>
+        <v>4342</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>1363</v>
+        <v>10234</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>2553</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>14871</v>
+        <v>18333</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>4440</v>
+        <v>18313</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>7822</v>
+        <v>21873</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>11773</v>
+        <v>4314</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>3639</v>
+        <v>8360</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>21336</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>3790</v>
+        <v>9198</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>12532</v>
+        <v>5716</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>4774</v>
+        <v>2961</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>4172</v>
+        <v>6132</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>7780</v>
+        <v>3929</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>6102</v>
+        <v>27271</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>6100</v>
+        <v>7957</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>8617</v>
+        <v>8893</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>1587</v>
+        <v>10032</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>14070</v>
+        <v>7408</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>5924</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>13732</v>
+        <v>10396</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>9024</v>
+        <v>8098</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>2937</v>
+        <v>4399</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>12613</v>
+        <v>5741</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>24891</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>9326</v>
+        <v>6112</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>2428</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>8151</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>26089</v>
+        <v>6536</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>7108</v>
+        <v>8201</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>5605</v>
+        <v>8997</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>2520</v>
+        <v>3048</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>5268</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>4318</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>12446</v>
+        <v>5615</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>536</v>
+        <v>9774</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>6692</v>
+        <v>8363</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>5743</v>
+        <v>7710</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>6849</v>
+        <v>4484</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>14712</v>
+        <v>11169</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>3613</v>
+        <v>12110</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>4533</v>
+        <v>3936</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>2756</v>
+        <v>19881</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>4296</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>1826</v>
+        <v>10596</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>12611</v>
+        <v>3286</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>7491</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>6236</v>
+        <v>7557</v>
       </c>
     </row>
   </sheetData>
@@ -960,1102 +960,1102 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>4621</v>
+        <v>4172</v>
       </c>
       <c r="B2">
-        <v>77.016666666666666</v>
+        <v>69.533333333333331</v>
       </c>
       <c r="C2">
-        <v>1.283611111111111</v>
+        <v>1.1588888888888889</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>9307</v>
+        <v>4562</v>
       </c>
       <c r="B3">
-        <v>155.11666666666667</v>
+        <v>76.033333333333331</v>
       </c>
       <c r="C3">
-        <v>2.5852777777777778</v>
+        <v>1.2672222222222222</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>1919</v>
+        <v>4322</v>
       </c>
       <c r="B4">
-        <v>31.983333333333334</v>
+        <v>72.033333333333331</v>
       </c>
       <c r="C4">
-        <v>0.5330555555555555</v>
+        <v>1.2005555555555556</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>2046</v>
+        <v>7782</v>
       </c>
       <c r="B5">
-        <v>34.1</v>
+        <v>129.69999999999999</v>
       </c>
       <c r="C5">
-        <v>0.56833333333333336</v>
+        <v>2.1616666666666666</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>4033</v>
+        <v>10876</v>
       </c>
       <c r="B6">
-        <v>67.216666666666669</v>
+        <v>181.26666666666668</v>
       </c>
       <c r="C6">
-        <v>1.1202777777777777</v>
+        <v>3.0211111111111113</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>11206</v>
+        <v>5951</v>
       </c>
       <c r="B7">
-        <v>186.76666666666668</v>
+        <v>99.183333333333337</v>
       </c>
       <c r="C7">
-        <v>3.1127777777777776</v>
+        <v>1.6530555555555555</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>3268</v>
+        <v>12391</v>
       </c>
       <c r="B8">
-        <v>54.466666666666669</v>
+        <v>206.51666666666668</v>
       </c>
       <c r="C8">
-        <v>0.90777777777777779</v>
+        <v>3.4419444444444443</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>6429</v>
+        <v>6623</v>
       </c>
       <c r="B9">
-        <v>107.15</v>
+        <v>110.38333333333334</v>
       </c>
       <c r="C9">
-        <v>1.7858333333333334</v>
+        <v>1.8397222222222223</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>6984</v>
+        <v>5401</v>
       </c>
       <c r="B10">
-        <v>116.4</v>
+        <v>90.016666666666666</v>
       </c>
       <c r="C10">
-        <v>1.94</v>
+        <v>1.5002777777777778</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>12850</v>
+        <v>6899</v>
       </c>
       <c r="B11">
-        <v>214.16666666666666</v>
+        <v>114.98333333333333</v>
       </c>
       <c r="C11">
-        <v>3.5694444444444446</v>
+        <v>1.9163888888888889</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>3891</v>
+        <v>6561</v>
       </c>
       <c r="B12">
-        <v>64.849999999999994</v>
+        <v>109.35</v>
       </c>
       <c r="C12">
-        <v>1.0808333333333333</v>
+        <v>1.8225</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>3288</v>
+        <v>8902</v>
       </c>
       <c r="B13">
-        <v>54.8</v>
+        <v>148.36666666666667</v>
       </c>
       <c r="C13">
-        <v>0.91333333333333333</v>
+        <v>2.472777777777778</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>1533</v>
+        <v>4153</v>
       </c>
       <c r="B14">
-        <v>25.55</v>
+        <v>69.216666666666669</v>
       </c>
       <c r="C14">
-        <v>0.42583333333333334</v>
+        <v>1.1536111111111111</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>6961</v>
+        <v>5442</v>
       </c>
       <c r="B15">
-        <v>116.01666666666667</v>
+        <v>90.7</v>
       </c>
       <c r="C15">
-        <v>1.9336111111111112</v>
+        <v>1.5116666666666667</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>9003</v>
+        <v>20536</v>
       </c>
       <c r="B16">
-        <v>150.05000000000001</v>
+        <v>342.26666666666665</v>
       </c>
       <c r="C16">
-        <v>2.5008333333333335</v>
+        <v>5.7044444444444444</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>5071</v>
+        <v>8271</v>
       </c>
       <c r="B17">
-        <v>84.516666666666666</v>
+        <v>137.85</v>
       </c>
       <c r="C17">
-        <v>1.408611111111111</v>
+        <v>2.2974999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>16124</v>
+        <v>5069</v>
       </c>
       <c r="B18">
-        <v>268.73333333333335</v>
+        <v>84.483333333333334</v>
       </c>
       <c r="C18">
-        <v>4.4788888888888891</v>
+        <v>1.4080555555555556</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>10222</v>
+        <v>9490</v>
       </c>
       <c r="B19">
-        <v>170.36666666666667</v>
+        <v>158.16666666666666</v>
       </c>
       <c r="C19">
-        <v>2.8394444444444447</v>
+        <v>2.6361111111111111</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>7144</v>
+        <v>10777</v>
       </c>
       <c r="B20">
-        <v>119.06666666666666</v>
+        <v>179.61666666666667</v>
       </c>
       <c r="C20">
-        <v>1.9844444444444445</v>
+        <v>2.993611111111111</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>5012</v>
+        <v>7897</v>
       </c>
       <c r="B21">
-        <v>83.533333333333331</v>
+        <v>131.61666666666667</v>
       </c>
       <c r="C21">
-        <v>1.3922222222222222</v>
+        <v>2.1936111111111112</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>3129</v>
+        <v>3484</v>
       </c>
       <c r="B22">
-        <v>52.15</v>
+        <v>58.06666666666667</v>
       </c>
       <c r="C22">
-        <v>0.86916666666666664</v>
+        <v>0.96777777777777774</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>4995</v>
+        <v>16702</v>
       </c>
       <c r="B23">
-        <v>83.25</v>
+        <v>278.36666666666667</v>
       </c>
       <c r="C23">
-        <v>1.3875</v>
+        <v>4.639444444444444</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>6899</v>
+        <v>4945</v>
       </c>
       <c r="B24">
-        <v>114.98333333333333</v>
+        <v>82.416666666666671</v>
       </c>
       <c r="C24">
-        <v>1.9163888888888889</v>
+        <v>1.3736111111111111</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>14015</v>
+        <v>6493</v>
       </c>
       <c r="B25">
-        <v>233.58333333333334</v>
+        <v>108.21666666666667</v>
       </c>
       <c r="C25">
-        <v>3.8930555555555557</v>
+        <v>1.8036111111111111</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>1687</v>
+        <v>3877</v>
       </c>
       <c r="B26">
-        <v>28.116666666666667</v>
+        <v>64.61666666666666</v>
       </c>
       <c r="C26">
-        <v>0.46861111111111109</v>
+        <v>1.0769444444444445</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>6132</v>
+        <v>3922</v>
       </c>
       <c r="B27">
-        <v>102.2</v>
+        <v>65.36666666666666</v>
       </c>
       <c r="C27">
-        <v>1.7033333333333334</v>
+        <v>1.0894444444444444</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>5460</v>
+        <v>15518</v>
       </c>
       <c r="B28">
-        <v>91</v>
+        <v>258.63333333333333</v>
       </c>
       <c r="C28">
-        <v>1.5166666666666666</v>
+        <v>4.3105555555555553</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>5177</v>
+        <v>1973</v>
       </c>
       <c r="B29">
-        <v>86.283333333333331</v>
+        <v>32.883333333333333</v>
       </c>
       <c r="C29">
-        <v>1.4380555555555556</v>
+        <v>0.54805555555555552</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>9816</v>
+        <v>6150</v>
       </c>
       <c r="B30">
-        <v>163.6</v>
+        <v>102.5</v>
       </c>
       <c r="C30">
-        <v>2.7266666666666666</v>
+        <v>1.7083333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>9525</v>
+        <v>4528</v>
       </c>
       <c r="B31">
-        <v>158.75</v>
+        <v>75.466666666666669</v>
       </c>
       <c r="C31">
-        <v>2.6458333333333335</v>
+        <v>1.2577777777777779</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>8508</v>
+        <v>14678</v>
       </c>
       <c r="B32">
-        <v>141.80000000000001</v>
+        <v>244.63333333333333</v>
       </c>
       <c r="C32">
-        <v>2.3633333333333333</v>
+        <v>4.0772222222222219</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>11641</v>
+        <v>2824</v>
       </c>
       <c r="B33">
-        <v>194.01666666666668</v>
+        <v>47.06666666666667</v>
       </c>
       <c r="C33">
-        <v>3.2336111111111112</v>
+        <v>0.7844444444444445</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>5647</v>
+        <v>3380</v>
       </c>
       <c r="B34">
-        <v>94.11666666666666</v>
+        <v>56.333333333333336</v>
       </c>
       <c r="C34">
-        <v>1.5686111111111112</v>
+        <v>0.93888888888888888</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>18367</v>
+        <v>15302</v>
       </c>
       <c r="B35">
-        <v>306.11666666666667</v>
+        <v>255.03333333333333</v>
       </c>
       <c r="C35">
-        <v>5.1019444444444444</v>
+        <v>4.2505555555555556</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>10715</v>
+        <v>2571</v>
       </c>
       <c r="B36">
-        <v>178.58333333333334</v>
+        <v>42.85</v>
       </c>
       <c r="C36">
-        <v>2.9763888888888888</v>
+        <v>0.71416666666666662</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>3351</v>
+        <v>13442</v>
       </c>
       <c r="B37">
-        <v>55.85</v>
+        <v>224.03333333333333</v>
       </c>
       <c r="C37">
-        <v>0.93083333333333329</v>
+        <v>3.733888888888889</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>3079</v>
+        <v>3958</v>
       </c>
       <c r="B38">
-        <v>51.31666666666667</v>
+        <v>65.966666666666669</v>
       </c>
       <c r="C38">
-        <v>0.8552777777777778</v>
+        <v>1.0994444444444444</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>6130</v>
+        <v>6599</v>
       </c>
       <c r="B39">
-        <v>102.16666666666667</v>
+        <v>109.98333333333333</v>
       </c>
       <c r="C39">
-        <v>1.7027777777777777</v>
+        <v>1.8330555555555557</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>14350</v>
+        <v>8944</v>
       </c>
       <c r="B40">
-        <v>239.16666666666666</v>
+        <v>149.06666666666666</v>
       </c>
       <c r="C40">
-        <v>3.9861111111111112</v>
+        <v>2.4844444444444442</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>2793</v>
+        <v>9477</v>
       </c>
       <c r="B41">
-        <v>46.55</v>
+        <v>157.94999999999999</v>
       </c>
       <c r="C41">
-        <v>0.77583333333333337</v>
+        <v>2.6324999999999998</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>3014</v>
+        <v>4359</v>
       </c>
       <c r="B42">
-        <v>50.233333333333334</v>
+        <v>72.650000000000006</v>
       </c>
       <c r="C42">
-        <v>0.8372222222222222</v>
+        <v>1.2108333333333334</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>5409</v>
+        <v>5767</v>
       </c>
       <c r="B43">
-        <v>90.15</v>
+        <v>96.11666666666666</v>
       </c>
       <c r="C43">
-        <v>1.5024999999999999</v>
+        <v>1.6019444444444444</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>2491</v>
+        <v>8001</v>
       </c>
       <c r="B44">
-        <v>41.516666666666666</v>
+        <v>133.35</v>
       </c>
       <c r="C44">
-        <v>0.69194444444444447</v>
+        <v>2.2225000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>1764</v>
+        <v>23108</v>
       </c>
       <c r="B45">
-        <v>29.4</v>
+        <v>385.13333333333333</v>
       </c>
       <c r="C45">
-        <v>0.49</v>
+        <v>6.4188888888888886</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>44481</v>
+        <v>8586</v>
       </c>
       <c r="B46">
-        <v>741.35</v>
+        <v>143.1</v>
       </c>
       <c r="C46">
-        <v>12.355833333333333</v>
+        <v>2.3849999999999998</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>6197</v>
+        <v>3283</v>
       </c>
       <c r="B47">
-        <v>103.28333333333333</v>
+        <v>54.716666666666669</v>
       </c>
       <c r="C47">
-        <v>1.7213888888888889</v>
+        <v>0.91194444444444445</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>2970</v>
+        <v>2768</v>
       </c>
       <c r="B48">
-        <v>49.5</v>
+        <v>46.133333333333333</v>
       </c>
       <c r="C48">
-        <v>0.82499999999999996</v>
+        <v>0.76888888888888884</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>6317</v>
+        <v>6199</v>
       </c>
       <c r="B49">
-        <v>105.28333333333333</v>
+        <v>103.31666666666666</v>
       </c>
       <c r="C49">
-        <v>1.7547222222222223</v>
+        <v>1.7219444444444445</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>6136</v>
+        <v>9403</v>
       </c>
       <c r="B50">
-        <v>102.26666666666667</v>
+        <v>156.71666666666667</v>
       </c>
       <c r="C50">
-        <v>1.7044444444444444</v>
+        <v>2.6119444444444446</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>2815</v>
+        <v>18052</v>
       </c>
       <c r="B51">
-        <v>46.916666666666664</v>
+        <v>300.86666666666667</v>
       </c>
       <c r="C51">
-        <v>0.78194444444444444</v>
+        <v>5.014444444444444</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>8107</v>
+        <v>2797</v>
       </c>
       <c r="B52">
-        <v>135.11666666666667</v>
+        <v>46.616666666666667</v>
       </c>
       <c r="C52">
-        <v>2.2519444444444443</v>
+        <v>0.77694444444444444</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>5353</v>
+        <v>3237</v>
       </c>
       <c r="B53">
-        <v>89.216666666666669</v>
+        <v>53.95</v>
       </c>
       <c r="C53">
-        <v>1.4869444444444444</v>
+        <v>0.89916666666666667</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>1557</v>
+        <v>4342</v>
       </c>
       <c r="B54">
-        <v>25.95</v>
+        <v>72.36666666666666</v>
       </c>
       <c r="C54">
-        <v>0.4325</v>
+        <v>1.2061111111111111</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>1363</v>
+        <v>10234</v>
       </c>
       <c r="B55">
-        <v>22.716666666666665</v>
+        <v>170.56666666666666</v>
       </c>
       <c r="C55">
-        <v>0.37861111111111112</v>
+        <v>2.8427777777777776</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>2553</v>
+        <v>4232</v>
       </c>
       <c r="B56">
-        <v>42.55</v>
+        <v>70.533333333333331</v>
       </c>
       <c r="C56">
-        <v>0.70916666666666661</v>
+        <v>1.1755555555555555</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>14871</v>
+        <v>18333</v>
       </c>
       <c r="B57">
-        <v>247.85</v>
+        <v>305.55</v>
       </c>
       <c r="C57">
-        <v>4.1308333333333334</v>
+        <v>5.0925000000000002</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>4440</v>
+        <v>18313</v>
       </c>
       <c r="B58">
-        <v>74</v>
+        <v>305.21666666666664</v>
       </c>
       <c r="C58">
-        <v>1.2333333333333334</v>
+        <v>5.0869444444444447</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>7822</v>
+        <v>21873</v>
       </c>
       <c r="B59">
-        <v>130.36666666666667</v>
+        <v>364.55</v>
       </c>
       <c r="C59">
-        <v>2.1727777777777777</v>
+        <v>6.0758333333333336</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>11773</v>
+        <v>4314</v>
       </c>
       <c r="B60">
-        <v>196.21666666666667</v>
+        <v>71.900000000000006</v>
       </c>
       <c r="C60">
-        <v>3.2702777777777778</v>
+        <v>1.1983333333333333</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>3639</v>
+        <v>8360</v>
       </c>
       <c r="B61">
-        <v>60.65</v>
+        <v>139.33333333333334</v>
       </c>
       <c r="C61">
-        <v>1.0108333333333333</v>
+        <v>2.3222222222222224</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>21336</v>
+        <v>2660</v>
       </c>
       <c r="B62">
-        <v>355.6</v>
+        <v>44.333333333333336</v>
       </c>
       <c r="C62">
-        <v>5.9266666666666667</v>
+        <v>0.73888888888888893</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>3790</v>
+        <v>9198</v>
       </c>
       <c r="B63">
-        <v>63.166666666666664</v>
+        <v>153.30000000000001</v>
       </c>
       <c r="C63">
-        <v>1.0527777777777778</v>
+        <v>2.5550000000000002</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>12532</v>
+        <v>5716</v>
       </c>
       <c r="B64">
-        <v>208.86666666666667</v>
+        <v>95.266666666666666</v>
       </c>
       <c r="C64">
-        <v>3.4811111111111113</v>
+        <v>1.5877777777777777</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>4774</v>
+        <v>2961</v>
       </c>
       <c r="B65">
-        <v>79.566666666666663</v>
+        <v>49.35</v>
       </c>
       <c r="C65">
-        <v>1.326111111111111</v>
+        <v>0.82250000000000001</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>4172</v>
+        <v>6132</v>
       </c>
       <c r="B66">
-        <v>69.533333333333331</v>
+        <v>102.2</v>
       </c>
       <c r="C66">
-        <v>1.1588888888888889</v>
+        <v>1.7033333333333334</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>7780</v>
+        <v>3929</v>
       </c>
       <c r="B67">
-        <v>129.66666666666666</v>
+        <v>65.483333333333334</v>
       </c>
       <c r="C67">
-        <v>2.161111111111111</v>
+        <v>1.091388888888889</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>6102</v>
+        <v>27271</v>
       </c>
       <c r="B68">
-        <v>101.7</v>
+        <v>454.51666666666665</v>
       </c>
       <c r="C68">
-        <v>1.6950000000000001</v>
+        <v>7.575277777777778</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>6100</v>
+        <v>7957</v>
       </c>
       <c r="B69">
-        <v>101.66666666666667</v>
+        <v>132.61666666666667</v>
       </c>
       <c r="C69">
-        <v>1.6944444444444444</v>
+        <v>2.2102777777777778</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>8617</v>
+        <v>8893</v>
       </c>
       <c r="B70">
-        <v>143.61666666666667</v>
+        <v>148.21666666666667</v>
       </c>
       <c r="C70">
-        <v>2.3936111111111109</v>
+        <v>2.4702777777777776</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>1587</v>
+        <v>10032</v>
       </c>
       <c r="B71">
-        <v>26.45</v>
+        <v>167.2</v>
       </c>
       <c r="C71">
-        <v>0.44083333333333335</v>
+        <v>2.7866666666666666</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>14070</v>
+        <v>7408</v>
       </c>
       <c r="B72">
-        <v>234.5</v>
+        <v>123.46666666666667</v>
       </c>
       <c r="C72">
-        <v>3.9083333333333332</v>
+        <v>2.0577777777777779</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>5924</v>
+        <v>1118</v>
       </c>
       <c r="B73">
-        <v>98.733333333333334</v>
+        <v>18.633333333333333</v>
       </c>
       <c r="C73">
-        <v>1.6455555555555557</v>
+        <v>0.31055555555555553</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>13732</v>
+        <v>10396</v>
       </c>
       <c r="B74">
-        <v>228.86666666666667</v>
+        <v>173.26666666666668</v>
       </c>
       <c r="C74">
-        <v>3.8144444444444443</v>
+        <v>2.887777777777778</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>9024</v>
+        <v>8098</v>
       </c>
       <c r="B75">
-        <v>150.4</v>
+        <v>134.96666666666667</v>
       </c>
       <c r="C75">
-        <v>2.5066666666666668</v>
+        <v>2.2494444444444444</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>2937</v>
+        <v>4399</v>
       </c>
       <c r="B76">
-        <v>48.95</v>
+        <v>73.316666666666663</v>
       </c>
       <c r="C76">
-        <v>0.8158333333333333</v>
+        <v>1.2219444444444445</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>12613</v>
+        <v>5741</v>
       </c>
       <c r="B77">
-        <v>210.21666666666667</v>
+        <v>95.683333333333337</v>
       </c>
       <c r="C77">
-        <v>3.5036111111111112</v>
+        <v>1.5947222222222222</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>24891</v>
+        <v>1997</v>
       </c>
       <c r="B78">
-        <v>414.85</v>
+        <v>33.283333333333331</v>
       </c>
       <c r="C78">
-        <v>6.9141666666666666</v>
+        <v>0.55472222222222223</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>9326</v>
+        <v>6112</v>
       </c>
       <c r="B79">
-        <v>155.43333333333334</v>
+        <v>101.86666666666666</v>
       </c>
       <c r="C79">
-        <v>2.5905555555555555</v>
+        <v>1.6977777777777778</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>2428</v>
+        <v>2267</v>
       </c>
       <c r="B80">
-        <v>40.466666666666669</v>
+        <v>37.783333333333331</v>
       </c>
       <c r="C80">
-        <v>0.6744444444444444</v>
+        <v>0.62972222222222218</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>8151</v>
+        <v>2579</v>
       </c>
       <c r="B81">
-        <v>135.85</v>
+        <v>42.983333333333334</v>
       </c>
       <c r="C81">
-        <v>2.2641666666666667</v>
+        <v>0.71638888888888885</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>26089</v>
+        <v>6536</v>
       </c>
       <c r="B82">
-        <v>434.81666666666666</v>
+        <v>108.93333333333334</v>
       </c>
       <c r="C82">
-        <v>7.2469444444444449</v>
+        <v>1.8155555555555556</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>7108</v>
+        <v>8201</v>
       </c>
       <c r="B83">
-        <v>118.46666666666667</v>
+        <v>136.68333333333334</v>
       </c>
       <c r="C83">
-        <v>1.9744444444444444</v>
+        <v>2.2780555555555555</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>5605</v>
+        <v>8997</v>
       </c>
       <c r="B84">
-        <v>93.416666666666671</v>
+        <v>149.94999999999999</v>
       </c>
       <c r="C84">
-        <v>1.5569444444444445</v>
+        <v>2.4991666666666665</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>2520</v>
+        <v>3048</v>
       </c>
       <c r="B85">
-        <v>42</v>
+        <v>50.8</v>
       </c>
       <c r="C85">
-        <v>0.7</v>
+        <v>0.84666666666666668</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>5268</v>
+        <v>1369</v>
       </c>
       <c r="B86">
-        <v>87.8</v>
+        <v>22.816666666666666</v>
       </c>
       <c r="C86">
-        <v>1.4633333333333334</v>
+        <v>0.38027777777777777</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>4318</v>
+        <v>2506</v>
       </c>
       <c r="B87">
-        <v>71.966666666666669</v>
+        <v>41.766666666666666</v>
       </c>
       <c r="C87">
-        <v>1.1994444444444445</v>
+        <v>0.69611111111111112</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>12446</v>
+        <v>5615</v>
       </c>
       <c r="B88">
-        <v>207.43333333333334</v>
+        <v>93.583333333333329</v>
       </c>
       <c r="C88">
-        <v>3.4572222222222222</v>
+        <v>1.5597222222222222</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>536</v>
+        <v>9774</v>
       </c>
       <c r="B89">
-        <v>8.9333333333333336</v>
+        <v>162.9</v>
       </c>
       <c r="C89">
-        <v>0.14888888888888888</v>
+        <v>2.7149999999999999</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>6692</v>
+        <v>8363</v>
       </c>
       <c r="B90">
-        <v>111.53333333333333</v>
+        <v>139.38333333333333</v>
       </c>
       <c r="C90">
-        <v>1.8588888888888888</v>
+        <v>2.3230555555555554</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>5743</v>
+        <v>7710</v>
       </c>
       <c r="B91">
-        <v>95.716666666666669</v>
+        <v>128.5</v>
       </c>
       <c r="C91">
-        <v>1.5952777777777778</v>
+        <v>2.1416666666666666</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>6849</v>
+        <v>4484</v>
       </c>
       <c r="B92">
-        <v>114.15</v>
+        <v>74.733333333333334</v>
       </c>
       <c r="C92">
-        <v>1.9025000000000001</v>
+        <v>1.2455555555555555</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>14712</v>
+        <v>11169</v>
       </c>
       <c r="B93">
-        <v>245.2</v>
+        <v>186.15</v>
       </c>
       <c r="C93">
-        <v>4.0866666666666669</v>
+        <v>3.1025</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>3613</v>
+        <v>12110</v>
       </c>
       <c r="B94">
-        <v>60.216666666666669</v>
+        <v>201.83333333333334</v>
       </c>
       <c r="C94">
-        <v>1.003611111111111</v>
+        <v>3.3638888888888889</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>4533</v>
+        <v>3936</v>
       </c>
       <c r="B95">
-        <v>75.55</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="C95">
-        <v>1.2591666666666668</v>
+        <v>1.0933333333333333</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>2756</v>
+        <v>19881</v>
       </c>
       <c r="B96">
-        <v>45.93333333333333</v>
+        <v>331.35</v>
       </c>
       <c r="C96">
-        <v>0.76555555555555554</v>
+        <v>5.5225</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>4296</v>
+        <v>3937</v>
       </c>
       <c r="B97">
-        <v>71.599999999999994</v>
+        <v>65.61666666666666</v>
       </c>
       <c r="C97">
-        <v>1.1933333333333334</v>
+        <v>1.0936111111111111</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>1826</v>
+        <v>10596</v>
       </c>
       <c r="B98">
-        <v>30.433333333333334</v>
+        <v>176.6</v>
       </c>
       <c r="C98">
-        <v>0.50722222222222224</v>
+        <v>2.9433333333333334</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>12611</v>
+        <v>3286</v>
       </c>
       <c r="B99">
-        <v>210.18333333333334</v>
+        <v>54.766666666666666</v>
       </c>
       <c r="C99">
-        <v>3.5030555555555556</v>
+        <v>0.9127777777777778</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>7491</v>
+        <v>1919</v>
       </c>
       <c r="B100">
-        <v>124.85</v>
+        <v>31.983333333333334</v>
       </c>
       <c r="C100">
-        <v>2.0808333333333335</v>
+        <v>0.5330555555555555</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>6236</v>
+        <v>7557</v>
       </c>
       <c r="B101">
-        <v>103.93333333333334</v>
+        <v>125.95</v>
       </c>
       <c r="C101">
-        <v>1.7322222222222223</v>
+        <v>2.0991666666666666</v>
       </c>
     </row>
   </sheetData>

--- a/Time to Fixation Experiments - Changing Chemotaxis Equation/Experiment 1 - Testing Fixation Time/Time_for_Bac_Fix_Pos50_Start.xlsx
+++ b/Time to Fixation Experiments - Changing Chemotaxis Equation/Experiment 1 - Testing Fixation Time/Time_for_Bac_Fix_Pos50_Start.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\Time to Fixation Experiments - Changing Chemotaxis Equation\Experiment 1 - Testing Fixation Time\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{431272C5-D09C-482B-A84B-5972162A8044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{627F1B7C-813C-448D-B97D-4AC1854A32DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C5D5DF43-D68A-448F-BEE9-BC751A2734F3}"/>
   </bookViews>
@@ -437,500 +437,800 @@
       <c r="A2">
         <v>4172</v>
       </c>
+      <c r="B2">
+        <v>4172</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>4562</v>
       </c>
+      <c r="B3">
+        <v>4562</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>4322</v>
       </c>
+      <c r="B4">
+        <v>4322</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>7782</v>
       </c>
+      <c r="B5">
+        <v>7326</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>10876</v>
       </c>
+      <c r="B6">
+        <v>12048</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5951</v>
       </c>
+      <c r="B7">
+        <v>5336</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>12391</v>
       </c>
+      <c r="B8">
+        <v>6565</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6623</v>
       </c>
+      <c r="B9">
+        <v>6275</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>5401</v>
       </c>
+      <c r="B10">
+        <v>7969</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>6899</v>
       </c>
+      <c r="B11">
+        <v>3786</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>6561</v>
       </c>
+      <c r="B12">
+        <v>3328</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>8902</v>
       </c>
+      <c r="B13">
+        <v>13556</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>4153</v>
       </c>
+      <c r="B14">
+        <v>5012</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>5442</v>
       </c>
+      <c r="B15">
+        <v>7691</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>20536</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <v>5028</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>8271</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>18286</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>5069</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9490</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <v>12058</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>10777</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <v>3805</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>7897</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <v>18045</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>3484</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <v>6176</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>16702</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <v>5387</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>4945</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>6493</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B25">
+        <v>4531</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>3877</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B26">
+        <v>7608</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>3922</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B27">
+        <v>4376</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>15518</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B28">
+        <v>4257</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>1973</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B29">
+        <v>11382</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>6150</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B30">
+        <v>8072</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>4528</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B31">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>14678</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B32">
+        <v>8552</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2824</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B33">
+        <v>2763</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>3380</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B34">
+        <v>8498</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>15302</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B35">
+        <v>6121</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2571</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B36">
+        <v>2994</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>13442</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B37">
+        <v>3813</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>3958</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B38">
+        <v>4216</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>6599</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B39">
+        <v>6629</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>8944</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B40">
+        <v>7943</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>9477</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B41">
+        <v>11518</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>4359</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B42">
+        <v>3735</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>5767</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B43">
+        <v>5533</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>8001</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B44">
+        <v>10244</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>23108</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B45">
+        <v>4378</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>8586</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B46">
+        <v>4118</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>3283</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B47">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2768</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B48">
+        <v>5618</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>6199</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B49">
+        <v>13135</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>9403</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B50">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>18052</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+        <v>4172</v>
+      </c>
+      <c r="B51">
+        <v>4159</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2797</v>
       </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B52">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>3237</v>
       </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B53">
+        <v>12801</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>4342</v>
       </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B54">
+        <v>5698</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>10234</v>
       </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B55">
+        <v>8958</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>4232</v>
       </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B56">
+        <v>5455</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>18333</v>
       </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B57">
+        <v>3134</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>18313</v>
       </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B58">
+        <v>5022</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>21873</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+        <v>4322</v>
+      </c>
+      <c r="B59">
+        <v>10345</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>4314</v>
       </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B60">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>8360</v>
       </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B61">
+        <v>9557</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2660</v>
       </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B62">
+        <v>9578</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>9198</v>
       </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B63">
+        <v>3413</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>5716</v>
       </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B64">
+        <v>11804</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>2961</v>
       </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B65">
+        <v>17299</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>6132</v>
       </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B66">
+        <v>9940</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>3929</v>
       </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B67">
+        <v>4185</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>27271</v>
       </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B68">
+        <v>4214</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>7957</v>
       </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B69">
+        <v>4853</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>8893</v>
       </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B70">
+        <v>3857</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>10032</v>
       </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B71">
+        <v>14386</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>7408</v>
       </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B72">
+        <v>6377</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>1118</v>
       </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B73">
+        <v>4942</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>10396</v>
       </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B74">
+        <v>9667</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>8098</v>
       </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B75">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>4399</v>
       </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B76">
+        <v>4231</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>5741</v>
       </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B77">
+        <v>3207</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>1997</v>
       </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B78">
+        <v>6991</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>6112</v>
       </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B79">
+        <v>12951</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>2267</v>
       </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B80">
+        <v>5939</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>2579</v>
       </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B81">
+        <v>3549</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>6536</v>
       </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B82">
+        <v>22178</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>8201</v>
       </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B83">
+        <v>3598</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>8997</v>
       </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B84">
+        <v>9764</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>3048</v>
       </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B85">
+        <v>6748</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>1369</v>
       </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B86">
+        <v>6079</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>2506</v>
       </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B87">
+        <v>5289</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>5615</v>
       </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B88">
+        <v>6430</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>9774</v>
       </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B89">
+        <v>10501</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>8363</v>
       </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B90">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>7710</v>
       </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B91">
+        <v>10340</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>4484</v>
       </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B92">
+        <v>4578</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>11169</v>
       </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B93">
+        <v>5188</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>12110</v>
       </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B94">
+        <v>4503</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>3936</v>
       </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B95">
+        <v>5797</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>19881</v>
       </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B96">
+        <v>17511</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>3937</v>
       </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B97">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>10596</v>
       </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B98">
+        <v>4621</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>3286</v>
       </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B99">
+        <v>6064</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>1919</v>
       </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B100">
+        <v>2910</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>7557</v>
+      </c>
+      <c r="B101">
+        <v>7520</v>
       </c>
     </row>
   </sheetData>
@@ -1499,13 +1799,13 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>18052</v>
+        <v>4172</v>
       </c>
       <c r="B51">
-        <v>300.86666666666667</v>
+        <v>69.533333333333331</v>
       </c>
       <c r="C51">
-        <v>5.014444444444444</v>
+        <v>1.1588888888888889</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1587,13 +1887,13 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>21873</v>
+        <v>4322</v>
       </c>
       <c r="B59">
-        <v>364.55</v>
+        <v>72.033333333333331</v>
       </c>
       <c r="C59">
-        <v>6.0758333333333336</v>
+        <v>1.2005555555555556</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -2065,7 +2365,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63B6A8E3-D8EB-4280-840A-346B01586132}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -2081,6 +2381,1106 @@
       </c>
       <c r="C1" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>4172</v>
+      </c>
+      <c r="B2">
+        <v>69.533333333333331</v>
+      </c>
+      <c r="C2">
+        <v>1.1588888888888889</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>4562</v>
+      </c>
+      <c r="B3">
+        <v>76.033333333333331</v>
+      </c>
+      <c r="C3">
+        <v>1.2672222222222222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>4322</v>
+      </c>
+      <c r="B4">
+        <v>72.033333333333331</v>
+      </c>
+      <c r="C4">
+        <v>1.2005555555555556</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>7326</v>
+      </c>
+      <c r="B5">
+        <v>122.1</v>
+      </c>
+      <c r="C5">
+        <v>2.0350000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>12048</v>
+      </c>
+      <c r="B6">
+        <v>200.8</v>
+      </c>
+      <c r="C6">
+        <v>3.3466666666666667</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>5336</v>
+      </c>
+      <c r="B7">
+        <v>88.933333333333337</v>
+      </c>
+      <c r="C7">
+        <v>1.4822222222222223</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>6565</v>
+      </c>
+      <c r="B8">
+        <v>109.41666666666667</v>
+      </c>
+      <c r="C8">
+        <v>1.8236111111111111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>6275</v>
+      </c>
+      <c r="B9">
+        <v>104.58333333333333</v>
+      </c>
+      <c r="C9">
+        <v>1.7430555555555556</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>7969</v>
+      </c>
+      <c r="B10">
+        <v>132.81666666666666</v>
+      </c>
+      <c r="C10">
+        <v>2.2136111111111112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>3786</v>
+      </c>
+      <c r="B11">
+        <v>63.1</v>
+      </c>
+      <c r="C11">
+        <v>1.0516666666666667</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>3328</v>
+      </c>
+      <c r="B12">
+        <v>55.466666666666669</v>
+      </c>
+      <c r="C12">
+        <v>0.9244444444444444</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>13556</v>
+      </c>
+      <c r="B13">
+        <v>225.93333333333334</v>
+      </c>
+      <c r="C13">
+        <v>3.7655555555555558</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>5012</v>
+      </c>
+      <c r="B14">
+        <v>83.533333333333331</v>
+      </c>
+      <c r="C14">
+        <v>1.3922222222222222</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>7691</v>
+      </c>
+      <c r="B15">
+        <v>128.18333333333334</v>
+      </c>
+      <c r="C15">
+        <v>2.1363888888888889</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>5028</v>
+      </c>
+      <c r="B16">
+        <v>83.8</v>
+      </c>
+      <c r="C16">
+        <v>1.3966666666666667</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>18286</v>
+      </c>
+      <c r="B17">
+        <v>304.76666666666665</v>
+      </c>
+      <c r="C17">
+        <v>5.0794444444444444</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2016</v>
+      </c>
+      <c r="B18">
+        <v>33.6</v>
+      </c>
+      <c r="C18">
+        <v>0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>12058</v>
+      </c>
+      <c r="B19">
+        <v>200.96666666666667</v>
+      </c>
+      <c r="C19">
+        <v>3.3494444444444444</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>3805</v>
+      </c>
+      <c r="B20">
+        <v>63.416666666666664</v>
+      </c>
+      <c r="C20">
+        <v>1.0569444444444445</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>18045</v>
+      </c>
+      <c r="B21">
+        <v>300.75</v>
+      </c>
+      <c r="C21">
+        <v>5.0125000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>6176</v>
+      </c>
+      <c r="B22">
+        <v>102.93333333333334</v>
+      </c>
+      <c r="C22">
+        <v>1.7155555555555555</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>5387</v>
+      </c>
+      <c r="B23">
+        <v>89.783333333333331</v>
+      </c>
+      <c r="C23">
+        <v>1.496388888888889</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2023</v>
+      </c>
+      <c r="B24">
+        <v>33.716666666666669</v>
+      </c>
+      <c r="C24">
+        <v>0.56194444444444447</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>4531</v>
+      </c>
+      <c r="B25">
+        <v>75.516666666666666</v>
+      </c>
+      <c r="C25">
+        <v>1.2586111111111111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>7608</v>
+      </c>
+      <c r="B26">
+        <v>126.8</v>
+      </c>
+      <c r="C26">
+        <v>2.1133333333333333</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>4376</v>
+      </c>
+      <c r="B27">
+        <v>72.933333333333337</v>
+      </c>
+      <c r="C27">
+        <v>1.2155555555555555</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>4257</v>
+      </c>
+      <c r="B28">
+        <v>70.95</v>
+      </c>
+      <c r="C28">
+        <v>1.1825000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>11382</v>
+      </c>
+      <c r="B29">
+        <v>189.7</v>
+      </c>
+      <c r="C29">
+        <v>3.1616666666666666</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>8072</v>
+      </c>
+      <c r="B30">
+        <v>134.53333333333333</v>
+      </c>
+      <c r="C30">
+        <v>2.2422222222222223</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>6177</v>
+      </c>
+      <c r="B31">
+        <v>102.95</v>
+      </c>
+      <c r="C31">
+        <v>1.7158333333333333</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>8552</v>
+      </c>
+      <c r="B32">
+        <v>142.53333333333333</v>
+      </c>
+      <c r="C32">
+        <v>2.3755555555555556</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>2763</v>
+      </c>
+      <c r="B33">
+        <v>46.05</v>
+      </c>
+      <c r="C33">
+        <v>0.76749999999999996</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>8498</v>
+      </c>
+      <c r="B34">
+        <v>141.63333333333333</v>
+      </c>
+      <c r="C34">
+        <v>2.3605555555555555</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>6121</v>
+      </c>
+      <c r="B35">
+        <v>102.01666666666667</v>
+      </c>
+      <c r="C35">
+        <v>1.7002777777777778</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>2994</v>
+      </c>
+      <c r="B36">
+        <v>49.9</v>
+      </c>
+      <c r="C36">
+        <v>0.83166666666666667</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>3813</v>
+      </c>
+      <c r="B37">
+        <v>63.55</v>
+      </c>
+      <c r="C37">
+        <v>1.0591666666666666</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>4216</v>
+      </c>
+      <c r="B38">
+        <v>70.266666666666666</v>
+      </c>
+      <c r="C38">
+        <v>1.1711111111111112</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>6629</v>
+      </c>
+      <c r="B39">
+        <v>110.48333333333333</v>
+      </c>
+      <c r="C39">
+        <v>1.841388888888889</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>7943</v>
+      </c>
+      <c r="B40">
+        <v>132.38333333333333</v>
+      </c>
+      <c r="C40">
+        <v>2.2063888888888887</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>11518</v>
+      </c>
+      <c r="B41">
+        <v>191.96666666666667</v>
+      </c>
+      <c r="C41">
+        <v>3.1994444444444445</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>3735</v>
+      </c>
+      <c r="B42">
+        <v>62.25</v>
+      </c>
+      <c r="C42">
+        <v>1.0375000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>5533</v>
+      </c>
+      <c r="B43">
+        <v>92.216666666666669</v>
+      </c>
+      <c r="C43">
+        <v>1.5369444444444444</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>10244</v>
+      </c>
+      <c r="B44">
+        <v>170.73333333333332</v>
+      </c>
+      <c r="C44">
+        <v>2.8455555555555554</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>4378</v>
+      </c>
+      <c r="B45">
+        <v>72.966666666666669</v>
+      </c>
+      <c r="C45">
+        <v>1.2161111111111111</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>4118</v>
+      </c>
+      <c r="B46">
+        <v>68.63333333333334</v>
+      </c>
+      <c r="C46">
+        <v>1.143888888888889</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>2042</v>
+      </c>
+      <c r="B47">
+        <v>34.033333333333331</v>
+      </c>
+      <c r="C47">
+        <v>0.56722222222222218</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>5618</v>
+      </c>
+      <c r="B48">
+        <v>93.63333333333334</v>
+      </c>
+      <c r="C48">
+        <v>1.5605555555555555</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>13135</v>
+      </c>
+      <c r="B49">
+        <v>218.91666666666666</v>
+      </c>
+      <c r="C49">
+        <v>3.6486111111111112</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>4003</v>
+      </c>
+      <c r="B50">
+        <v>66.716666666666669</v>
+      </c>
+      <c r="C50">
+        <v>1.1119444444444444</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>4159</v>
+      </c>
+      <c r="B51">
+        <v>69.316666666666663</v>
+      </c>
+      <c r="C51">
+        <v>1.1552777777777778</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>2037</v>
+      </c>
+      <c r="B52">
+        <v>33.950000000000003</v>
+      </c>
+      <c r="C52">
+        <v>0.5658333333333333</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>12801</v>
+      </c>
+      <c r="B53">
+        <v>213.35</v>
+      </c>
+      <c r="C53">
+        <v>3.5558333333333332</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>5698</v>
+      </c>
+      <c r="B54">
+        <v>94.966666666666669</v>
+      </c>
+      <c r="C54">
+        <v>1.5827777777777778</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>8958</v>
+      </c>
+      <c r="B55">
+        <v>149.30000000000001</v>
+      </c>
+      <c r="C55">
+        <v>2.4883333333333333</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>5455</v>
+      </c>
+      <c r="B56">
+        <v>90.916666666666671</v>
+      </c>
+      <c r="C56">
+        <v>1.5152777777777777</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>3134</v>
+      </c>
+      <c r="B57">
+        <v>52.233333333333334</v>
+      </c>
+      <c r="C57">
+        <v>0.87055555555555553</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>5022</v>
+      </c>
+      <c r="B58">
+        <v>83.7</v>
+      </c>
+      <c r="C58">
+        <v>1.395</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>10345</v>
+      </c>
+      <c r="B59">
+        <v>172.41666666666666</v>
+      </c>
+      <c r="C59">
+        <v>2.8736111111111109</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>4880</v>
+      </c>
+      <c r="B60">
+        <v>81.333333333333329</v>
+      </c>
+      <c r="C60">
+        <v>1.3555555555555556</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>9557</v>
+      </c>
+      <c r="B61">
+        <v>159.28333333333333</v>
+      </c>
+      <c r="C61">
+        <v>2.6547222222222224</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>9578</v>
+      </c>
+      <c r="B62">
+        <v>159.63333333333333</v>
+      </c>
+      <c r="C62">
+        <v>2.6605555555555553</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>3413</v>
+      </c>
+      <c r="B63">
+        <v>56.883333333333333</v>
+      </c>
+      <c r="C63">
+        <v>0.94805555555555554</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>11804</v>
+      </c>
+      <c r="B64">
+        <v>196.73333333333332</v>
+      </c>
+      <c r="C64">
+        <v>3.278888888888889</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>17299</v>
+      </c>
+      <c r="B65">
+        <v>288.31666666666666</v>
+      </c>
+      <c r="C65">
+        <v>4.8052777777777775</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>9940</v>
+      </c>
+      <c r="B66">
+        <v>165.66666666666666</v>
+      </c>
+      <c r="C66">
+        <v>2.7611111111111111</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>4185</v>
+      </c>
+      <c r="B67">
+        <v>69.75</v>
+      </c>
+      <c r="C67">
+        <v>1.1625000000000001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>4214</v>
+      </c>
+      <c r="B68">
+        <v>70.233333333333334</v>
+      </c>
+      <c r="C68">
+        <v>1.1705555555555556</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>4853</v>
+      </c>
+      <c r="B69">
+        <v>80.88333333333334</v>
+      </c>
+      <c r="C69">
+        <v>1.3480555555555556</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>3857</v>
+      </c>
+      <c r="B70">
+        <v>64.283333333333331</v>
+      </c>
+      <c r="C70">
+        <v>1.0713888888888889</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>14386</v>
+      </c>
+      <c r="B71">
+        <v>239.76666666666668</v>
+      </c>
+      <c r="C71">
+        <v>3.9961111111111109</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>6377</v>
+      </c>
+      <c r="B72">
+        <v>106.28333333333333</v>
+      </c>
+      <c r="C72">
+        <v>1.7713888888888889</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>4942</v>
+      </c>
+      <c r="B73">
+        <v>82.36666666666666</v>
+      </c>
+      <c r="C73">
+        <v>1.3727777777777779</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>9667</v>
+      </c>
+      <c r="B74">
+        <v>161.11666666666667</v>
+      </c>
+      <c r="C74">
+        <v>2.6852777777777779</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>2532</v>
+      </c>
+      <c r="B75">
+        <v>42.2</v>
+      </c>
+      <c r="C75">
+        <v>0.70333333333333337</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>4231</v>
+      </c>
+      <c r="B76">
+        <v>70.516666666666666</v>
+      </c>
+      <c r="C76">
+        <v>1.1752777777777779</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>3207</v>
+      </c>
+      <c r="B77">
+        <v>53.45</v>
+      </c>
+      <c r="C77">
+        <v>0.89083333333333337</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>6991</v>
+      </c>
+      <c r="B78">
+        <v>116.51666666666667</v>
+      </c>
+      <c r="C78">
+        <v>1.9419444444444445</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>12951</v>
+      </c>
+      <c r="B79">
+        <v>215.85</v>
+      </c>
+      <c r="C79">
+        <v>3.5975000000000001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>5939</v>
+      </c>
+      <c r="B80">
+        <v>98.983333333333334</v>
+      </c>
+      <c r="C80">
+        <v>1.6497222222222223</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>3549</v>
+      </c>
+      <c r="B81">
+        <v>59.15</v>
+      </c>
+      <c r="C81">
+        <v>0.98583333333333334</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>22178</v>
+      </c>
+      <c r="B82">
+        <v>369.63333333333333</v>
+      </c>
+      <c r="C82">
+        <v>6.1605555555555558</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>3598</v>
+      </c>
+      <c r="B83">
+        <v>59.966666666666669</v>
+      </c>
+      <c r="C83">
+        <v>0.99944444444444447</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>9764</v>
+      </c>
+      <c r="B84">
+        <v>162.73333333333332</v>
+      </c>
+      <c r="C84">
+        <v>2.7122222222222221</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>6748</v>
+      </c>
+      <c r="B85">
+        <v>112.46666666666667</v>
+      </c>
+      <c r="C85">
+        <v>1.8744444444444444</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>6079</v>
+      </c>
+      <c r="B86">
+        <v>101.31666666666666</v>
+      </c>
+      <c r="C86">
+        <v>1.6886111111111111</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>5289</v>
+      </c>
+      <c r="B87">
+        <v>88.15</v>
+      </c>
+      <c r="C87">
+        <v>1.4691666666666667</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>6430</v>
+      </c>
+      <c r="B88">
+        <v>107.16666666666667</v>
+      </c>
+      <c r="C88">
+        <v>1.7861111111111112</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>10501</v>
+      </c>
+      <c r="B89">
+        <v>175.01666666666668</v>
+      </c>
+      <c r="C89">
+        <v>2.9169444444444443</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>7554</v>
+      </c>
+      <c r="B90">
+        <v>125.9</v>
+      </c>
+      <c r="C90">
+        <v>2.0983333333333332</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>10340</v>
+      </c>
+      <c r="B91">
+        <v>172.33333333333334</v>
+      </c>
+      <c r="C91">
+        <v>2.8722222222222222</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>4578</v>
+      </c>
+      <c r="B92">
+        <v>76.3</v>
+      </c>
+      <c r="C92">
+        <v>1.2716666666666667</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>5188</v>
+      </c>
+      <c r="B93">
+        <v>86.466666666666669</v>
+      </c>
+      <c r="C93">
+        <v>1.441111111111111</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>4503</v>
+      </c>
+      <c r="B94">
+        <v>75.05</v>
+      </c>
+      <c r="C94">
+        <v>1.2508333333333332</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>5797</v>
+      </c>
+      <c r="B95">
+        <v>96.61666666666666</v>
+      </c>
+      <c r="C95">
+        <v>1.6102777777777777</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>17511</v>
+      </c>
+      <c r="B96">
+        <v>291.85000000000002</v>
+      </c>
+      <c r="C96">
+        <v>4.8641666666666667</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>1817</v>
+      </c>
+      <c r="B97">
+        <v>30.283333333333335</v>
+      </c>
+      <c r="C97">
+        <v>0.50472222222222218</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>4621</v>
+      </c>
+      <c r="B98">
+        <v>77.016666666666666</v>
+      </c>
+      <c r="C98">
+        <v>1.283611111111111</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>6064</v>
+      </c>
+      <c r="B99">
+        <v>101.06666666666666</v>
+      </c>
+      <c r="C99">
+        <v>1.6844444444444444</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>2910</v>
+      </c>
+      <c r="B100">
+        <v>48.5</v>
+      </c>
+      <c r="C100">
+        <v>0.80833333333333335</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>7520</v>
+      </c>
+      <c r="B101">
+        <v>125.33333333333333</v>
+      </c>
+      <c r="C101">
+        <v>2.088888888888889</v>
       </c>
     </row>
   </sheetData>

--- a/Time to Fixation Experiments - Changing Chemotaxis Equation/Experiment 1 - Testing Fixation Time/Time_for_Bac_Fix_Pos50_Start.xlsx
+++ b/Time to Fixation Experiments - Changing Chemotaxis Equation/Experiment 1 - Testing Fixation Time/Time_for_Bac_Fix_Pos50_Start.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\Time to Fixation Experiments - Changing Chemotaxis Equation\Experiment 1 - Testing Fixation Time\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{627F1B7C-813C-448D-B97D-4AC1854A32DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CDF4672-DA27-4F64-A5C1-6001219A8814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C5D5DF43-D68A-448F-BEE9-BC751A2734F3}"/>
   </bookViews>
@@ -435,802 +435,802 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>4172</v>
+        <v>3124</v>
       </c>
       <c r="B2">
-        <v>4172</v>
+        <v>3396</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>4562</v>
+        <v>6104</v>
       </c>
       <c r="B3">
-        <v>4562</v>
+        <v>6099</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>4322</v>
+        <v>3418</v>
       </c>
       <c r="B4">
-        <v>4322</v>
+        <v>3482</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>7782</v>
+        <v>4620</v>
       </c>
       <c r="B5">
-        <v>7326</v>
+        <v>4762</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>10876</v>
+        <v>4282</v>
       </c>
       <c r="B6">
-        <v>12048</v>
+        <v>4366</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>5951</v>
+        <v>4547</v>
       </c>
       <c r="B7">
-        <v>5336</v>
+        <v>5558</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>12391</v>
+        <v>2715</v>
       </c>
       <c r="B8">
-        <v>6565</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>6623</v>
+        <v>4243</v>
       </c>
       <c r="B9">
-        <v>6275</v>
+        <v>4127</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>5401</v>
+        <v>3978</v>
       </c>
       <c r="B10">
-        <v>7969</v>
+        <v>4162</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>6899</v>
+        <v>5629</v>
       </c>
       <c r="B11">
-        <v>3786</v>
+        <v>4479</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>6561</v>
+        <v>5299</v>
       </c>
       <c r="B12">
-        <v>3328</v>
+        <v>5818</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>8902</v>
+        <v>6230</v>
       </c>
       <c r="B13">
-        <v>13556</v>
+        <v>7763</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>4153</v>
+        <v>5523</v>
       </c>
       <c r="B14">
-        <v>5012</v>
+        <v>6338</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>5442</v>
+        <v>4696</v>
       </c>
       <c r="B15">
-        <v>7691</v>
+        <v>6178</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>20536</v>
+        <v>6213</v>
       </c>
       <c r="B16">
-        <v>5028</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>8271</v>
+        <v>3267</v>
       </c>
       <c r="B17">
-        <v>18286</v>
+        <v>5154</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>5069</v>
+        <v>4544</v>
       </c>
       <c r="B18">
-        <v>2016</v>
+        <v>5867</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>9490</v>
+        <v>5881</v>
       </c>
       <c r="B19">
-        <v>12058</v>
+        <v>6106</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>10777</v>
+        <v>2160</v>
       </c>
       <c r="B20">
-        <v>3805</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>7897</v>
+        <v>8622</v>
       </c>
       <c r="B21">
-        <v>18045</v>
+        <v>6670</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>3484</v>
+        <v>6049</v>
       </c>
       <c r="B22">
-        <v>6176</v>
+        <v>6245</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>16702</v>
+        <v>2186</v>
       </c>
       <c r="B23">
-        <v>5387</v>
+        <v>6914</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>4945</v>
+        <v>6236</v>
       </c>
       <c r="B24">
-        <v>2023</v>
+        <v>6727</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>6493</v>
+        <v>2035</v>
       </c>
       <c r="B25">
-        <v>4531</v>
+        <v>4708</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>3877</v>
+        <v>4360</v>
       </c>
       <c r="B26">
-        <v>7608</v>
+        <v>6313</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>3922</v>
+        <v>3470</v>
       </c>
       <c r="B27">
-        <v>4376</v>
+        <v>4411</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>15518</v>
+        <v>4732</v>
       </c>
       <c r="B28">
-        <v>4257</v>
+        <v>4863</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>1973</v>
+        <v>2726</v>
       </c>
       <c r="B29">
-        <v>11382</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>6150</v>
+        <v>4280</v>
       </c>
       <c r="B30">
-        <v>8072</v>
+        <v>4822</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>4528</v>
+        <v>2723</v>
       </c>
       <c r="B31">
-        <v>6177</v>
+        <v>3494</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>14678</v>
+        <v>6551</v>
       </c>
       <c r="B32">
-        <v>8552</v>
+        <v>7230</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>2824</v>
+        <v>6015</v>
       </c>
       <c r="B33">
-        <v>2763</v>
+        <v>6262</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>3380</v>
+        <v>9707</v>
       </c>
       <c r="B34">
-        <v>8498</v>
+        <v>12163</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>15302</v>
+        <v>4402</v>
       </c>
       <c r="B35">
-        <v>6121</v>
+        <v>6460</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>2571</v>
+        <v>5667</v>
       </c>
       <c r="B36">
-        <v>2994</v>
+        <v>6116</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>13442</v>
+        <v>1747</v>
       </c>
       <c r="B37">
-        <v>3813</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>3958</v>
+        <v>3447</v>
       </c>
       <c r="B38">
-        <v>4216</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>6599</v>
+        <v>3903</v>
       </c>
       <c r="B39">
-        <v>6629</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>8944</v>
+        <v>12265</v>
       </c>
       <c r="B40">
-        <v>7943</v>
+        <v>8876</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>9477</v>
+        <v>6677</v>
       </c>
       <c r="B41">
-        <v>11518</v>
+        <v>8042</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>4359</v>
+        <v>4105</v>
       </c>
       <c r="B42">
-        <v>3735</v>
+        <v>4905</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>5767</v>
+        <v>2687</v>
       </c>
       <c r="B43">
-        <v>5533</v>
+        <v>4801</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>8001</v>
+        <v>10349</v>
       </c>
       <c r="B44">
-        <v>10244</v>
+        <v>11579</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>23108</v>
+        <v>3533</v>
       </c>
       <c r="B45">
-        <v>4378</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>8586</v>
+        <v>5366</v>
       </c>
       <c r="B46">
-        <v>4118</v>
+        <v>5556</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>3283</v>
+        <v>1657</v>
       </c>
       <c r="B47">
-        <v>2042</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>2768</v>
+        <v>2160</v>
       </c>
       <c r="B48">
-        <v>5618</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>6199</v>
+        <v>3151</v>
       </c>
       <c r="B49">
-        <v>13135</v>
+        <v>3508</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>9403</v>
+        <v>2632</v>
       </c>
       <c r="B50">
-        <v>4003</v>
+        <v>5261</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>4172</v>
+        <v>8063</v>
       </c>
       <c r="B51">
-        <v>4159</v>
+        <v>4313</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>2797</v>
+        <v>3230</v>
       </c>
       <c r="B52">
-        <v>2037</v>
+        <v>3385</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>3237</v>
+        <v>11772</v>
       </c>
       <c r="B53">
-        <v>12801</v>
+        <v>14358</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>4342</v>
+        <v>2003</v>
       </c>
       <c r="B54">
-        <v>5698</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>10234</v>
+        <v>2308</v>
       </c>
       <c r="B55">
-        <v>8958</v>
+        <v>5513</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>4232</v>
+        <v>6843</v>
       </c>
       <c r="B56">
-        <v>5455</v>
+        <v>7544</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>18333</v>
+        <v>5814</v>
       </c>
       <c r="B57">
-        <v>3134</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>18313</v>
+        <v>3359</v>
       </c>
       <c r="B58">
-        <v>5022</v>
+        <v>5577</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>4322</v>
+        <v>4836</v>
       </c>
       <c r="B59">
-        <v>10345</v>
+        <v>4918</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>4314</v>
+        <v>4548</v>
       </c>
       <c r="B60">
-        <v>4880</v>
+        <v>5332</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>8360</v>
+        <v>3180</v>
       </c>
       <c r="B61">
-        <v>9557</v>
+        <v>3637</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>2660</v>
+        <v>9341</v>
       </c>
       <c r="B62">
-        <v>9578</v>
+        <v>9821</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>9198</v>
+        <v>11437</v>
       </c>
       <c r="B63">
-        <v>3413</v>
+        <v>8146</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>5716</v>
+        <v>5092</v>
       </c>
       <c r="B64">
-        <v>11804</v>
+        <v>5274</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>2961</v>
+        <v>2705</v>
       </c>
       <c r="B65">
-        <v>17299</v>
+        <v>2985</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>6132</v>
+        <v>3467</v>
       </c>
       <c r="B66">
-        <v>9940</v>
+        <v>4164</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>3929</v>
+        <v>4518</v>
       </c>
       <c r="B67">
-        <v>4185</v>
+        <v>7304</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>27271</v>
+        <v>4810</v>
       </c>
       <c r="B68">
-        <v>4214</v>
+        <v>4840</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>7957</v>
+        <v>8017</v>
       </c>
       <c r="B69">
-        <v>4853</v>
+        <v>4460</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>8893</v>
+        <v>3756</v>
       </c>
       <c r="B70">
-        <v>3857</v>
+        <v>4555</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>10032</v>
+        <v>2862</v>
       </c>
       <c r="B71">
-        <v>14386</v>
+        <v>3603</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>7408</v>
+        <v>2309</v>
       </c>
       <c r="B72">
-        <v>6377</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>1118</v>
+        <v>2581</v>
       </c>
       <c r="B73">
-        <v>4942</v>
+        <v>5448</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>10396</v>
+        <v>3459</v>
       </c>
       <c r="B74">
-        <v>9667</v>
+        <v>3609</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>8098</v>
+        <v>5216</v>
       </c>
       <c r="B75">
-        <v>2532</v>
+        <v>5556</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>4399</v>
+        <v>6289</v>
       </c>
       <c r="B76">
-        <v>4231</v>
+        <v>10096</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>5741</v>
+        <v>4316</v>
       </c>
       <c r="B77">
-        <v>3207</v>
+        <v>4655</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>1997</v>
+        <v>2103</v>
       </c>
       <c r="B78">
-        <v>6991</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>6112</v>
+        <v>4591</v>
       </c>
       <c r="B79">
-        <v>12951</v>
+        <v>6653</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>2267</v>
+        <v>2689</v>
       </c>
       <c r="B80">
-        <v>5939</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>2579</v>
+        <v>4617</v>
       </c>
       <c r="B81">
-        <v>3549</v>
+        <v>15319</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>6536</v>
+        <v>6601</v>
       </c>
       <c r="B82">
-        <v>22178</v>
+        <v>5593</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>8201</v>
+        <v>4410</v>
       </c>
       <c r="B83">
-        <v>3598</v>
+        <v>6585</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>8997</v>
+        <v>7618</v>
       </c>
       <c r="B84">
-        <v>9764</v>
+        <v>9823</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>3048</v>
+        <v>4001</v>
       </c>
       <c r="B85">
-        <v>6748</v>
+        <v>3996</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>1369</v>
+        <v>4764</v>
       </c>
       <c r="B86">
-        <v>6079</v>
+        <v>9721</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>2506</v>
+        <v>6739</v>
       </c>
       <c r="B87">
-        <v>5289</v>
+        <v>7629</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>5615</v>
+        <v>2293</v>
       </c>
       <c r="B88">
-        <v>6430</v>
+        <v>2920</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>9774</v>
+        <v>5812</v>
       </c>
       <c r="B89">
-        <v>10501</v>
+        <v>6460</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>8363</v>
+        <v>3764</v>
       </c>
       <c r="B90">
-        <v>7554</v>
+        <v>4990</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>7710</v>
+        <v>4049</v>
       </c>
       <c r="B91">
-        <v>10340</v>
+        <v>4696</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>4484</v>
+        <v>3241</v>
       </c>
       <c r="B92">
-        <v>4578</v>
+        <v>3243</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>11169</v>
+        <v>8723</v>
       </c>
       <c r="B93">
-        <v>5188</v>
+        <v>7174</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>12110</v>
+        <v>5224</v>
       </c>
       <c r="B94">
-        <v>4503</v>
+        <v>5224</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>3936</v>
+        <v>1854</v>
       </c>
       <c r="B95">
-        <v>5797</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>19881</v>
+        <v>3883</v>
       </c>
       <c r="B96">
-        <v>17511</v>
+        <v>5154</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>3937</v>
+        <v>5321</v>
       </c>
       <c r="B97">
-        <v>1817</v>
+        <v>5334</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>10596</v>
+        <v>1952</v>
       </c>
       <c r="B98">
-        <v>4621</v>
+        <v>3473</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>3286</v>
+        <v>5412</v>
       </c>
       <c r="B99">
-        <v>6064</v>
+        <v>9228</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>1919</v>
+        <v>4658</v>
       </c>
       <c r="B100">
-        <v>2910</v>
+        <v>4889</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>7557</v>
+        <v>3266</v>
       </c>
       <c r="B101">
-        <v>7520</v>
+        <v>4356</v>
       </c>
     </row>
   </sheetData>
@@ -1260,1102 +1260,1102 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>4172</v>
+        <v>3124</v>
       </c>
       <c r="B2">
-        <v>69.533333333333331</v>
+        <v>52.06666666666667</v>
       </c>
       <c r="C2">
-        <v>1.1588888888888889</v>
+        <v>0.86777777777777776</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>4562</v>
+        <v>6104</v>
       </c>
       <c r="B3">
-        <v>76.033333333333331</v>
+        <v>101.73333333333333</v>
       </c>
       <c r="C3">
-        <v>1.2672222222222222</v>
+        <v>1.6955555555555555</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>4322</v>
+        <v>3418</v>
       </c>
       <c r="B4">
-        <v>72.033333333333331</v>
+        <v>56.966666666666669</v>
       </c>
       <c r="C4">
-        <v>1.2005555555555556</v>
+        <v>0.94944444444444442</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>7782</v>
+        <v>4620</v>
       </c>
       <c r="B5">
-        <v>129.69999999999999</v>
+        <v>77</v>
       </c>
       <c r="C5">
-        <v>2.1616666666666666</v>
+        <v>1.2833333333333334</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>10876</v>
+        <v>4282</v>
       </c>
       <c r="B6">
-        <v>181.26666666666668</v>
+        <v>71.36666666666666</v>
       </c>
       <c r="C6">
-        <v>3.0211111111111113</v>
+        <v>1.1894444444444445</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>5951</v>
+        <v>4547</v>
       </c>
       <c r="B7">
-        <v>99.183333333333337</v>
+        <v>75.783333333333331</v>
       </c>
       <c r="C7">
-        <v>1.6530555555555555</v>
+        <v>1.2630555555555556</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>12391</v>
+        <v>2715</v>
       </c>
       <c r="B8">
-        <v>206.51666666666668</v>
+        <v>45.25</v>
       </c>
       <c r="C8">
-        <v>3.4419444444444443</v>
+        <v>0.75416666666666665</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>6623</v>
+        <v>4243</v>
       </c>
       <c r="B9">
-        <v>110.38333333333334</v>
+        <v>70.716666666666669</v>
       </c>
       <c r="C9">
-        <v>1.8397222222222223</v>
+        <v>1.1786111111111111</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>5401</v>
+        <v>3978</v>
       </c>
       <c r="B10">
-        <v>90.016666666666666</v>
+        <v>66.3</v>
       </c>
       <c r="C10">
-        <v>1.5002777777777778</v>
+        <v>1.105</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>6899</v>
+        <v>5629</v>
       </c>
       <c r="B11">
-        <v>114.98333333333333</v>
+        <v>93.816666666666663</v>
       </c>
       <c r="C11">
-        <v>1.9163888888888889</v>
+        <v>1.5636111111111111</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>6561</v>
+        <v>5299</v>
       </c>
       <c r="B12">
-        <v>109.35</v>
+        <v>88.316666666666663</v>
       </c>
       <c r="C12">
-        <v>1.8225</v>
+        <v>1.4719444444444445</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>8902</v>
+        <v>6230</v>
       </c>
       <c r="B13">
-        <v>148.36666666666667</v>
+        <v>103.83333333333333</v>
       </c>
       <c r="C13">
-        <v>2.472777777777778</v>
+        <v>1.7305555555555556</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>4153</v>
+        <v>5523</v>
       </c>
       <c r="B14">
-        <v>69.216666666666669</v>
+        <v>92.05</v>
       </c>
       <c r="C14">
-        <v>1.1536111111111111</v>
+        <v>1.5341666666666667</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>5442</v>
+        <v>4696</v>
       </c>
       <c r="B15">
-        <v>90.7</v>
+        <v>78.266666666666666</v>
       </c>
       <c r="C15">
-        <v>1.5116666666666667</v>
+        <v>1.3044444444444445</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>20536</v>
+        <v>6213</v>
       </c>
       <c r="B16">
-        <v>342.26666666666665</v>
+        <v>103.55</v>
       </c>
       <c r="C16">
-        <v>5.7044444444444444</v>
+        <v>1.7258333333333333</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>8271</v>
+        <v>3267</v>
       </c>
       <c r="B17">
-        <v>137.85</v>
+        <v>54.45</v>
       </c>
       <c r="C17">
-        <v>2.2974999999999999</v>
+        <v>0.90749999999999997</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>5069</v>
+        <v>4544</v>
       </c>
       <c r="B18">
-        <v>84.483333333333334</v>
+        <v>75.733333333333334</v>
       </c>
       <c r="C18">
-        <v>1.4080555555555556</v>
+        <v>1.2622222222222221</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>9490</v>
+        <v>5881</v>
       </c>
       <c r="B19">
-        <v>158.16666666666666</v>
+        <v>98.016666666666666</v>
       </c>
       <c r="C19">
-        <v>2.6361111111111111</v>
+        <v>1.6336111111111111</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>10777</v>
+        <v>2160</v>
       </c>
       <c r="B20">
-        <v>179.61666666666667</v>
+        <v>36</v>
       </c>
       <c r="C20">
-        <v>2.993611111111111</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>7897</v>
+        <v>8622</v>
       </c>
       <c r="B21">
-        <v>131.61666666666667</v>
+        <v>143.69999999999999</v>
       </c>
       <c r="C21">
-        <v>2.1936111111111112</v>
+        <v>2.395</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>3484</v>
+        <v>6049</v>
       </c>
       <c r="B22">
-        <v>58.06666666666667</v>
+        <v>100.81666666666666</v>
       </c>
       <c r="C22">
-        <v>0.96777777777777774</v>
+        <v>1.6802777777777778</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>16702</v>
+        <v>2186</v>
       </c>
       <c r="B23">
-        <v>278.36666666666667</v>
+        <v>36.43333333333333</v>
       </c>
       <c r="C23">
-        <v>4.639444444444444</v>
+        <v>0.60722222222222222</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>4945</v>
+        <v>6236</v>
       </c>
       <c r="B24">
-        <v>82.416666666666671</v>
+        <v>103.93333333333334</v>
       </c>
       <c r="C24">
-        <v>1.3736111111111111</v>
+        <v>1.7322222222222223</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>6493</v>
+        <v>2035</v>
       </c>
       <c r="B25">
-        <v>108.21666666666667</v>
+        <v>33.916666666666664</v>
       </c>
       <c r="C25">
-        <v>1.8036111111111111</v>
+        <v>0.56527777777777777</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>3877</v>
+        <v>4360</v>
       </c>
       <c r="B26">
-        <v>64.61666666666666</v>
+        <v>72.666666666666671</v>
       </c>
       <c r="C26">
-        <v>1.0769444444444445</v>
+        <v>1.211111111111111</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>3922</v>
+        <v>3470</v>
       </c>
       <c r="B27">
-        <v>65.36666666666666</v>
+        <v>57.833333333333336</v>
       </c>
       <c r="C27">
-        <v>1.0894444444444444</v>
+        <v>0.96388888888888891</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>15518</v>
+        <v>4732</v>
       </c>
       <c r="B28">
-        <v>258.63333333333333</v>
+        <v>78.86666666666666</v>
       </c>
       <c r="C28">
-        <v>4.3105555555555553</v>
+        <v>1.3144444444444445</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>1973</v>
+        <v>2726</v>
       </c>
       <c r="B29">
-        <v>32.883333333333333</v>
+        <v>45.43333333333333</v>
       </c>
       <c r="C29">
-        <v>0.54805555555555552</v>
+        <v>0.75722222222222224</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>6150</v>
+        <v>4280</v>
       </c>
       <c r="B30">
-        <v>102.5</v>
+        <v>71.333333333333329</v>
       </c>
       <c r="C30">
-        <v>1.7083333333333333</v>
+        <v>1.1888888888888889</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>4528</v>
+        <v>2723</v>
       </c>
       <c r="B31">
-        <v>75.466666666666669</v>
+        <v>45.383333333333333</v>
       </c>
       <c r="C31">
-        <v>1.2577777777777779</v>
+        <v>0.75638888888888889</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>14678</v>
+        <v>6551</v>
       </c>
       <c r="B32">
-        <v>244.63333333333333</v>
+        <v>109.18333333333334</v>
       </c>
       <c r="C32">
-        <v>4.0772222222222219</v>
+        <v>1.8197222222222222</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>2824</v>
+        <v>6015</v>
       </c>
       <c r="B33">
-        <v>47.06666666666667</v>
+        <v>100.25</v>
       </c>
       <c r="C33">
-        <v>0.7844444444444445</v>
+        <v>1.6708333333333334</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>3380</v>
+        <v>9707</v>
       </c>
       <c r="B34">
-        <v>56.333333333333336</v>
+        <v>161.78333333333333</v>
       </c>
       <c r="C34">
-        <v>0.93888888888888888</v>
+        <v>2.6963888888888889</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>15302</v>
+        <v>4402</v>
       </c>
       <c r="B35">
-        <v>255.03333333333333</v>
+        <v>73.36666666666666</v>
       </c>
       <c r="C35">
-        <v>4.2505555555555556</v>
+        <v>1.2227777777777777</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>2571</v>
+        <v>5667</v>
       </c>
       <c r="B36">
-        <v>42.85</v>
+        <v>94.45</v>
       </c>
       <c r="C36">
-        <v>0.71416666666666662</v>
+        <v>1.5741666666666667</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>13442</v>
+        <v>1747</v>
       </c>
       <c r="B37">
-        <v>224.03333333333333</v>
+        <v>29.116666666666667</v>
       </c>
       <c r="C37">
-        <v>3.733888888888889</v>
+        <v>0.48527777777777775</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>3958</v>
+        <v>3447</v>
       </c>
       <c r="B38">
-        <v>65.966666666666669</v>
+        <v>57.45</v>
       </c>
       <c r="C38">
-        <v>1.0994444444444444</v>
+        <v>0.95750000000000002</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>6599</v>
+        <v>3903</v>
       </c>
       <c r="B39">
-        <v>109.98333333333333</v>
+        <v>65.05</v>
       </c>
       <c r="C39">
-        <v>1.8330555555555557</v>
+        <v>1.0841666666666667</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>8944</v>
+        <v>12265</v>
       </c>
       <c r="B40">
-        <v>149.06666666666666</v>
+        <v>204.41666666666666</v>
       </c>
       <c r="C40">
-        <v>2.4844444444444442</v>
+        <v>3.4069444444444446</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>9477</v>
+        <v>6677</v>
       </c>
       <c r="B41">
-        <v>157.94999999999999</v>
+        <v>111.28333333333333</v>
       </c>
       <c r="C41">
-        <v>2.6324999999999998</v>
+        <v>1.8547222222222222</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>4359</v>
+        <v>4105</v>
       </c>
       <c r="B42">
-        <v>72.650000000000006</v>
+        <v>68.416666666666671</v>
       </c>
       <c r="C42">
-        <v>1.2108333333333334</v>
+        <v>1.1402777777777777</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>5767</v>
+        <v>2687</v>
       </c>
       <c r="B43">
-        <v>96.11666666666666</v>
+        <v>44.783333333333331</v>
       </c>
       <c r="C43">
-        <v>1.6019444444444444</v>
+        <v>0.74638888888888888</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>8001</v>
+        <v>10349</v>
       </c>
       <c r="B44">
-        <v>133.35</v>
+        <v>172.48333333333332</v>
       </c>
       <c r="C44">
-        <v>2.2225000000000001</v>
+        <v>2.8747222222222222</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>23108</v>
+        <v>3533</v>
       </c>
       <c r="B45">
-        <v>385.13333333333333</v>
+        <v>58.883333333333333</v>
       </c>
       <c r="C45">
-        <v>6.4188888888888886</v>
+        <v>0.98138888888888887</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>8586</v>
+        <v>5366</v>
       </c>
       <c r="B46">
-        <v>143.1</v>
+        <v>89.433333333333337</v>
       </c>
       <c r="C46">
-        <v>2.3849999999999998</v>
+        <v>1.4905555555555556</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>3283</v>
+        <v>1657</v>
       </c>
       <c r="B47">
-        <v>54.716666666666669</v>
+        <v>27.616666666666667</v>
       </c>
       <c r="C47">
-        <v>0.91194444444444445</v>
+        <v>0.46027777777777779</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>2768</v>
+        <v>2160</v>
       </c>
       <c r="B48">
-        <v>46.133333333333333</v>
+        <v>36</v>
       </c>
       <c r="C48">
-        <v>0.76888888888888884</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>6199</v>
+        <v>3151</v>
       </c>
       <c r="B49">
-        <v>103.31666666666666</v>
+        <v>52.516666666666666</v>
       </c>
       <c r="C49">
-        <v>1.7219444444444445</v>
+        <v>0.87527777777777782</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>9403</v>
+        <v>2632</v>
       </c>
       <c r="B50">
-        <v>156.71666666666667</v>
+        <v>43.866666666666667</v>
       </c>
       <c r="C50">
-        <v>2.6119444444444446</v>
+        <v>0.73111111111111116</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>4172</v>
+        <v>8063</v>
       </c>
       <c r="B51">
-        <v>69.533333333333331</v>
+        <v>134.38333333333333</v>
       </c>
       <c r="C51">
-        <v>1.1588888888888889</v>
+        <v>2.2397222222222224</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>2797</v>
+        <v>3230</v>
       </c>
       <c r="B52">
-        <v>46.616666666666667</v>
+        <v>53.833333333333336</v>
       </c>
       <c r="C52">
-        <v>0.77694444444444444</v>
+        <v>0.89722222222222225</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>3237</v>
+        <v>11772</v>
       </c>
       <c r="B53">
-        <v>53.95</v>
+        <v>196.2</v>
       </c>
       <c r="C53">
-        <v>0.89916666666666667</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>4342</v>
+        <v>2003</v>
       </c>
       <c r="B54">
-        <v>72.36666666666666</v>
+        <v>33.383333333333333</v>
       </c>
       <c r="C54">
-        <v>1.2061111111111111</v>
+        <v>0.55638888888888893</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>10234</v>
+        <v>2308</v>
       </c>
       <c r="B55">
-        <v>170.56666666666666</v>
+        <v>38.466666666666669</v>
       </c>
       <c r="C55">
-        <v>2.8427777777777776</v>
+        <v>0.64111111111111108</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>4232</v>
+        <v>6843</v>
       </c>
       <c r="B56">
-        <v>70.533333333333331</v>
+        <v>114.05</v>
       </c>
       <c r="C56">
-        <v>1.1755555555555555</v>
+        <v>1.9008333333333334</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>18333</v>
+        <v>5814</v>
       </c>
       <c r="B57">
-        <v>305.55</v>
+        <v>96.9</v>
       </c>
       <c r="C57">
-        <v>5.0925000000000002</v>
+        <v>1.615</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>18313</v>
+        <v>3359</v>
       </c>
       <c r="B58">
-        <v>305.21666666666664</v>
+        <v>55.983333333333334</v>
       </c>
       <c r="C58">
-        <v>5.0869444444444447</v>
+        <v>0.93305555555555553</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>4322</v>
+        <v>4836</v>
       </c>
       <c r="B59">
-        <v>72.033333333333331</v>
+        <v>80.599999999999994</v>
       </c>
       <c r="C59">
-        <v>1.2005555555555556</v>
+        <v>1.3433333333333333</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>4314</v>
+        <v>4548</v>
       </c>
       <c r="B60">
-        <v>71.900000000000006</v>
+        <v>75.8</v>
       </c>
       <c r="C60">
-        <v>1.1983333333333333</v>
+        <v>1.2633333333333334</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>8360</v>
+        <v>3180</v>
       </c>
       <c r="B61">
-        <v>139.33333333333334</v>
+        <v>53</v>
       </c>
       <c r="C61">
-        <v>2.3222222222222224</v>
+        <v>0.8833333333333333</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>2660</v>
+        <v>9341</v>
       </c>
       <c r="B62">
-        <v>44.333333333333336</v>
+        <v>155.68333333333334</v>
       </c>
       <c r="C62">
-        <v>0.73888888888888893</v>
+        <v>2.5947222222222224</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>9198</v>
+        <v>11437</v>
       </c>
       <c r="B63">
-        <v>153.30000000000001</v>
+        <v>190.61666666666667</v>
       </c>
       <c r="C63">
-        <v>2.5550000000000002</v>
+        <v>3.1769444444444446</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>5716</v>
+        <v>5092</v>
       </c>
       <c r="B64">
-        <v>95.266666666666666</v>
+        <v>84.86666666666666</v>
       </c>
       <c r="C64">
-        <v>1.5877777777777777</v>
+        <v>1.4144444444444444</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>2961</v>
+        <v>2705</v>
       </c>
       <c r="B65">
-        <v>49.35</v>
+        <v>45.083333333333336</v>
       </c>
       <c r="C65">
-        <v>0.82250000000000001</v>
+        <v>0.75138888888888888</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>6132</v>
+        <v>3467</v>
       </c>
       <c r="B66">
-        <v>102.2</v>
+        <v>57.783333333333331</v>
       </c>
       <c r="C66">
-        <v>1.7033333333333334</v>
+        <v>0.96305555555555555</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>3929</v>
+        <v>4518</v>
       </c>
       <c r="B67">
-        <v>65.483333333333334</v>
+        <v>75.3</v>
       </c>
       <c r="C67">
-        <v>1.091388888888889</v>
+        <v>1.2549999999999999</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>27271</v>
+        <v>4810</v>
       </c>
       <c r="B68">
-        <v>454.51666666666665</v>
+        <v>80.166666666666671</v>
       </c>
       <c r="C68">
-        <v>7.575277777777778</v>
+        <v>1.336111111111111</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>7957</v>
+        <v>8017</v>
       </c>
       <c r="B69">
-        <v>132.61666666666667</v>
+        <v>133.61666666666667</v>
       </c>
       <c r="C69">
-        <v>2.2102777777777778</v>
+        <v>2.2269444444444444</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>8893</v>
+        <v>3756</v>
       </c>
       <c r="B70">
-        <v>148.21666666666667</v>
+        <v>62.6</v>
       </c>
       <c r="C70">
-        <v>2.4702777777777776</v>
+        <v>1.0433333333333332</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>10032</v>
+        <v>2862</v>
       </c>
       <c r="B71">
-        <v>167.2</v>
+        <v>47.7</v>
       </c>
       <c r="C71">
-        <v>2.7866666666666666</v>
+        <v>0.79500000000000004</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>7408</v>
+        <v>2309</v>
       </c>
       <c r="B72">
-        <v>123.46666666666667</v>
+        <v>38.483333333333334</v>
       </c>
       <c r="C72">
-        <v>2.0577777777777779</v>
+        <v>0.6413888888888889</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>1118</v>
+        <v>2581</v>
       </c>
       <c r="B73">
-        <v>18.633333333333333</v>
+        <v>43.016666666666666</v>
       </c>
       <c r="C73">
-        <v>0.31055555555555553</v>
+        <v>0.7169444444444445</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>10396</v>
+        <v>3459</v>
       </c>
       <c r="B74">
-        <v>173.26666666666668</v>
+        <v>57.65</v>
       </c>
       <c r="C74">
-        <v>2.887777777777778</v>
+        <v>0.96083333333333332</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>8098</v>
+        <v>5216</v>
       </c>
       <c r="B75">
-        <v>134.96666666666667</v>
+        <v>86.933333333333337</v>
       </c>
       <c r="C75">
-        <v>2.2494444444444444</v>
+        <v>1.4488888888888889</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>4399</v>
+        <v>6289</v>
       </c>
       <c r="B76">
-        <v>73.316666666666663</v>
+        <v>104.81666666666666</v>
       </c>
       <c r="C76">
-        <v>1.2219444444444445</v>
+        <v>1.7469444444444444</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>5741</v>
+        <v>4316</v>
       </c>
       <c r="B77">
-        <v>95.683333333333337</v>
+        <v>71.933333333333337</v>
       </c>
       <c r="C77">
-        <v>1.5947222222222222</v>
+        <v>1.1988888888888889</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>1997</v>
+        <v>2103</v>
       </c>
       <c r="B78">
-        <v>33.283333333333331</v>
+        <v>35.049999999999997</v>
       </c>
       <c r="C78">
-        <v>0.55472222222222223</v>
+        <v>0.58416666666666661</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>6112</v>
+        <v>4591</v>
       </c>
       <c r="B79">
-        <v>101.86666666666666</v>
+        <v>76.516666666666666</v>
       </c>
       <c r="C79">
-        <v>1.6977777777777778</v>
+        <v>1.2752777777777777</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>2267</v>
+        <v>2689</v>
       </c>
       <c r="B80">
-        <v>37.783333333333331</v>
+        <v>44.81666666666667</v>
       </c>
       <c r="C80">
-        <v>0.62972222222222218</v>
+        <v>0.74694444444444441</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>2579</v>
+        <v>4617</v>
       </c>
       <c r="B81">
-        <v>42.983333333333334</v>
+        <v>76.95</v>
       </c>
       <c r="C81">
-        <v>0.71638888888888885</v>
+        <v>1.2825</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>6536</v>
+        <v>6601</v>
       </c>
       <c r="B82">
-        <v>108.93333333333334</v>
+        <v>110.01666666666667</v>
       </c>
       <c r="C82">
-        <v>1.8155555555555556</v>
+        <v>1.8336111111111111</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>8201</v>
+        <v>4410</v>
       </c>
       <c r="B83">
-        <v>136.68333333333334</v>
+        <v>73.5</v>
       </c>
       <c r="C83">
-        <v>2.2780555555555555</v>
+        <v>1.2250000000000001</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>8997</v>
+        <v>7618</v>
       </c>
       <c r="B84">
-        <v>149.94999999999999</v>
+        <v>126.96666666666667</v>
       </c>
       <c r="C84">
-        <v>2.4991666666666665</v>
+        <v>2.1161111111111111</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>3048</v>
+        <v>4001</v>
       </c>
       <c r="B85">
-        <v>50.8</v>
+        <v>66.683333333333337</v>
       </c>
       <c r="C85">
-        <v>0.84666666666666668</v>
+        <v>1.111388888888889</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>1369</v>
+        <v>4764</v>
       </c>
       <c r="B86">
-        <v>22.816666666666666</v>
+        <v>79.400000000000006</v>
       </c>
       <c r="C86">
-        <v>0.38027777777777777</v>
+        <v>1.3233333333333333</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>2506</v>
+        <v>6739</v>
       </c>
       <c r="B87">
-        <v>41.766666666666666</v>
+        <v>112.31666666666666</v>
       </c>
       <c r="C87">
-        <v>0.69611111111111112</v>
+        <v>1.8719444444444444</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>5615</v>
+        <v>2293</v>
       </c>
       <c r="B88">
-        <v>93.583333333333329</v>
+        <v>38.216666666666669</v>
       </c>
       <c r="C88">
-        <v>1.5597222222222222</v>
+        <v>0.63694444444444442</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>9774</v>
+        <v>5812</v>
       </c>
       <c r="B89">
-        <v>162.9</v>
+        <v>96.86666666666666</v>
       </c>
       <c r="C89">
-        <v>2.7149999999999999</v>
+        <v>1.6144444444444443</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>8363</v>
+        <v>3764</v>
       </c>
       <c r="B90">
-        <v>139.38333333333333</v>
+        <v>62.733333333333334</v>
       </c>
       <c r="C90">
-        <v>2.3230555555555554</v>
+        <v>1.0455555555555556</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>7710</v>
+        <v>4049</v>
       </c>
       <c r="B91">
-        <v>128.5</v>
+        <v>67.483333333333334</v>
       </c>
       <c r="C91">
-        <v>2.1416666666666666</v>
+        <v>1.1247222222222222</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>4484</v>
+        <v>3241</v>
       </c>
       <c r="B92">
-        <v>74.733333333333334</v>
+        <v>54.016666666666666</v>
       </c>
       <c r="C92">
-        <v>1.2455555555555555</v>
+        <v>0.90027777777777773</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>11169</v>
+        <v>8723</v>
       </c>
       <c r="B93">
-        <v>186.15</v>
+        <v>145.38333333333333</v>
       </c>
       <c r="C93">
-        <v>3.1025</v>
+        <v>2.4230555555555555</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>12110</v>
+        <v>5224</v>
       </c>
       <c r="B94">
-        <v>201.83333333333334</v>
+        <v>87.066666666666663</v>
       </c>
       <c r="C94">
-        <v>3.3638888888888889</v>
+        <v>1.451111111111111</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>3936</v>
+        <v>1854</v>
       </c>
       <c r="B95">
-        <v>65.599999999999994</v>
+        <v>30.9</v>
       </c>
       <c r="C95">
-        <v>1.0933333333333333</v>
+        <v>0.51500000000000001</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>19881</v>
+        <v>3883</v>
       </c>
       <c r="B96">
-        <v>331.35</v>
+        <v>64.716666666666669</v>
       </c>
       <c r="C96">
-        <v>5.5225</v>
+        <v>1.0786111111111112</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>3937</v>
+        <v>5321</v>
       </c>
       <c r="B97">
-        <v>65.61666666666666</v>
+        <v>88.683333333333337</v>
       </c>
       <c r="C97">
-        <v>1.0936111111111111</v>
+        <v>1.4780555555555555</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>10596</v>
+        <v>1952</v>
       </c>
       <c r="B98">
-        <v>176.6</v>
+        <v>32.533333333333331</v>
       </c>
       <c r="C98">
-        <v>2.9433333333333334</v>
+        <v>0.54222222222222227</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>3286</v>
+        <v>5412</v>
       </c>
       <c r="B99">
-        <v>54.766666666666666</v>
+        <v>90.2</v>
       </c>
       <c r="C99">
-        <v>0.9127777777777778</v>
+        <v>1.5033333333333334</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>1919</v>
+        <v>4658</v>
       </c>
       <c r="B100">
-        <v>31.983333333333334</v>
+        <v>77.63333333333334</v>
       </c>
       <c r="C100">
-        <v>0.5330555555555555</v>
+        <v>1.2938888888888889</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>7557</v>
+        <v>3266</v>
       </c>
       <c r="B101">
-        <v>125.95</v>
+        <v>54.43333333333333</v>
       </c>
       <c r="C101">
-        <v>2.0991666666666666</v>
+        <v>0.90722222222222226</v>
       </c>
     </row>
   </sheetData>
@@ -2385,1102 +2385,1102 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>4172</v>
+        <v>3396</v>
       </c>
       <c r="B2">
-        <v>69.533333333333331</v>
+        <v>56.6</v>
       </c>
       <c r="C2">
-        <v>1.1588888888888889</v>
+        <v>0.94333333333333336</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>4562</v>
+        <v>6099</v>
       </c>
       <c r="B3">
-        <v>76.033333333333331</v>
+        <v>101.65</v>
       </c>
       <c r="C3">
-        <v>1.2672222222222222</v>
+        <v>1.6941666666666666</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>4322</v>
+        <v>3482</v>
       </c>
       <c r="B4">
-        <v>72.033333333333331</v>
+        <v>58.033333333333331</v>
       </c>
       <c r="C4">
-        <v>1.2005555555555556</v>
+        <v>0.96722222222222221</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>7326</v>
+        <v>4762</v>
       </c>
       <c r="B5">
-        <v>122.1</v>
+        <v>79.36666666666666</v>
       </c>
       <c r="C5">
-        <v>2.0350000000000001</v>
+        <v>1.3227777777777778</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>12048</v>
+        <v>4366</v>
       </c>
       <c r="B6">
-        <v>200.8</v>
+        <v>72.766666666666666</v>
       </c>
       <c r="C6">
-        <v>3.3466666666666667</v>
+        <v>1.2127777777777777</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>5336</v>
+        <v>5558</v>
       </c>
       <c r="B7">
-        <v>88.933333333333337</v>
+        <v>92.63333333333334</v>
       </c>
       <c r="C7">
-        <v>1.4822222222222223</v>
+        <v>1.5438888888888889</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>6565</v>
+        <v>3240</v>
       </c>
       <c r="B8">
-        <v>109.41666666666667</v>
+        <v>54</v>
       </c>
       <c r="C8">
-        <v>1.8236111111111111</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>6275</v>
+        <v>4127</v>
       </c>
       <c r="B9">
-        <v>104.58333333333333</v>
+        <v>68.783333333333331</v>
       </c>
       <c r="C9">
-        <v>1.7430555555555556</v>
+        <v>1.1463888888888889</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>7969</v>
+        <v>4162</v>
       </c>
       <c r="B10">
-        <v>132.81666666666666</v>
+        <v>69.36666666666666</v>
       </c>
       <c r="C10">
-        <v>2.2136111111111112</v>
+        <v>1.1561111111111111</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>3786</v>
+        <v>4479</v>
       </c>
       <c r="B11">
-        <v>63.1</v>
+        <v>74.650000000000006</v>
       </c>
       <c r="C11">
-        <v>1.0516666666666667</v>
+        <v>1.2441666666666666</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>3328</v>
+        <v>5818</v>
       </c>
       <c r="B12">
-        <v>55.466666666666669</v>
+        <v>96.966666666666669</v>
       </c>
       <c r="C12">
-        <v>0.9244444444444444</v>
+        <v>1.6161111111111111</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>13556</v>
+        <v>7763</v>
       </c>
       <c r="B13">
-        <v>225.93333333333334</v>
+        <v>129.38333333333333</v>
       </c>
       <c r="C13">
-        <v>3.7655555555555558</v>
+        <v>2.1563888888888889</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>5012</v>
+        <v>6338</v>
       </c>
       <c r="B14">
-        <v>83.533333333333331</v>
+        <v>105.63333333333334</v>
       </c>
       <c r="C14">
-        <v>1.3922222222222222</v>
+        <v>1.7605555555555557</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>7691</v>
+        <v>6178</v>
       </c>
       <c r="B15">
-        <v>128.18333333333334</v>
+        <v>102.96666666666667</v>
       </c>
       <c r="C15">
-        <v>2.1363888888888889</v>
+        <v>1.7161111111111111</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>5028</v>
+        <v>5700</v>
       </c>
       <c r="B16">
-        <v>83.8</v>
+        <v>95</v>
       </c>
       <c r="C16">
-        <v>1.3966666666666667</v>
+        <v>1.5833333333333333</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>18286</v>
+        <v>5154</v>
       </c>
       <c r="B17">
-        <v>304.76666666666665</v>
+        <v>85.9</v>
       </c>
       <c r="C17">
-        <v>5.0794444444444444</v>
+        <v>1.4316666666666666</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>2016</v>
+        <v>5867</v>
       </c>
       <c r="B18">
-        <v>33.6</v>
+        <v>97.783333333333331</v>
       </c>
       <c r="C18">
-        <v>0.56000000000000005</v>
+        <v>1.6297222222222223</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>12058</v>
+        <v>6106</v>
       </c>
       <c r="B19">
-        <v>200.96666666666667</v>
+        <v>101.76666666666667</v>
       </c>
       <c r="C19">
-        <v>3.3494444444444444</v>
+        <v>1.6961111111111111</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>3805</v>
+        <v>2350</v>
       </c>
       <c r="B20">
-        <v>63.416666666666664</v>
+        <v>39.166666666666664</v>
       </c>
       <c r="C20">
-        <v>1.0569444444444445</v>
+        <v>0.65277777777777779</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>18045</v>
+        <v>6670</v>
       </c>
       <c r="B21">
-        <v>300.75</v>
+        <v>111.16666666666667</v>
       </c>
       <c r="C21">
-        <v>5.0125000000000002</v>
+        <v>1.8527777777777779</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>6176</v>
+        <v>6245</v>
       </c>
       <c r="B22">
-        <v>102.93333333333334</v>
+        <v>104.08333333333333</v>
       </c>
       <c r="C22">
-        <v>1.7155555555555555</v>
+        <v>1.7347222222222223</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>5387</v>
+        <v>6914</v>
       </c>
       <c r="B23">
-        <v>89.783333333333331</v>
+        <v>115.23333333333333</v>
       </c>
       <c r="C23">
-        <v>1.496388888888889</v>
+        <v>1.9205555555555556</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>2023</v>
+        <v>6727</v>
       </c>
       <c r="B24">
-        <v>33.716666666666669</v>
+        <v>112.11666666666666</v>
       </c>
       <c r="C24">
-        <v>0.56194444444444447</v>
+        <v>1.868611111111111</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>4531</v>
+        <v>4708</v>
       </c>
       <c r="B25">
-        <v>75.516666666666666</v>
+        <v>78.466666666666669</v>
       </c>
       <c r="C25">
-        <v>1.2586111111111111</v>
+        <v>1.3077777777777777</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>7608</v>
+        <v>6313</v>
       </c>
       <c r="B26">
-        <v>126.8</v>
+        <v>105.21666666666667</v>
       </c>
       <c r="C26">
-        <v>2.1133333333333333</v>
+        <v>1.753611111111111</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>4376</v>
+        <v>4411</v>
       </c>
       <c r="B27">
-        <v>72.933333333333337</v>
+        <v>73.516666666666666</v>
       </c>
       <c r="C27">
-        <v>1.2155555555555555</v>
+        <v>1.2252777777777777</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>4257</v>
+        <v>4863</v>
       </c>
       <c r="B28">
-        <v>70.95</v>
+        <v>81.05</v>
       </c>
       <c r="C28">
-        <v>1.1825000000000001</v>
+        <v>1.3508333333333333</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>11382</v>
+        <v>2728</v>
       </c>
       <c r="B29">
-        <v>189.7</v>
+        <v>45.466666666666669</v>
       </c>
       <c r="C29">
-        <v>3.1616666666666666</v>
+        <v>0.75777777777777777</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>8072</v>
+        <v>4822</v>
       </c>
       <c r="B30">
-        <v>134.53333333333333</v>
+        <v>80.36666666666666</v>
       </c>
       <c r="C30">
-        <v>2.2422222222222223</v>
+        <v>1.3394444444444444</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>6177</v>
+        <v>3494</v>
       </c>
       <c r="B31">
-        <v>102.95</v>
+        <v>58.233333333333334</v>
       </c>
       <c r="C31">
-        <v>1.7158333333333333</v>
+        <v>0.9705555555555555</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>8552</v>
+        <v>7230</v>
       </c>
       <c r="B32">
-        <v>142.53333333333333</v>
+        <v>120.5</v>
       </c>
       <c r="C32">
-        <v>2.3755555555555556</v>
+        <v>2.0083333333333333</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>2763</v>
+        <v>6262</v>
       </c>
       <c r="B33">
-        <v>46.05</v>
+        <v>104.36666666666666</v>
       </c>
       <c r="C33">
-        <v>0.76749999999999996</v>
+        <v>1.7394444444444443</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>8498</v>
+        <v>12163</v>
       </c>
       <c r="B34">
-        <v>141.63333333333333</v>
+        <v>202.71666666666667</v>
       </c>
       <c r="C34">
-        <v>2.3605555555555555</v>
+        <v>3.3786111111111112</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>6121</v>
+        <v>6460</v>
       </c>
       <c r="B35">
-        <v>102.01666666666667</v>
+        <v>107.66666666666667</v>
       </c>
       <c r="C35">
-        <v>1.7002777777777778</v>
+        <v>1.7944444444444445</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>2994</v>
+        <v>6116</v>
       </c>
       <c r="B36">
-        <v>49.9</v>
+        <v>101.93333333333334</v>
       </c>
       <c r="C36">
-        <v>0.83166666666666667</v>
+        <v>1.6988888888888889</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>3813</v>
+        <v>1919</v>
       </c>
       <c r="B37">
-        <v>63.55</v>
+        <v>31.983333333333334</v>
       </c>
       <c r="C37">
-        <v>1.0591666666666666</v>
+        <v>0.5330555555555555</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>4216</v>
+        <v>3862</v>
       </c>
       <c r="B38">
-        <v>70.266666666666666</v>
+        <v>64.36666666666666</v>
       </c>
       <c r="C38">
-        <v>1.1711111111111112</v>
+        <v>1.0727777777777778</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>6629</v>
+        <v>4247</v>
       </c>
       <c r="B39">
-        <v>110.48333333333333</v>
+        <v>70.783333333333331</v>
       </c>
       <c r="C39">
-        <v>1.841388888888889</v>
+        <v>1.1797222222222221</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>7943</v>
+        <v>8876</v>
       </c>
       <c r="B40">
-        <v>132.38333333333333</v>
+        <v>147.93333333333334</v>
       </c>
       <c r="C40">
-        <v>2.2063888888888887</v>
+        <v>2.4655555555555555</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>11518</v>
+        <v>8042</v>
       </c>
       <c r="B41">
-        <v>191.96666666666667</v>
+        <v>134.03333333333333</v>
       </c>
       <c r="C41">
-        <v>3.1994444444444445</v>
+        <v>2.233888888888889</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>3735</v>
+        <v>4905</v>
       </c>
       <c r="B42">
-        <v>62.25</v>
+        <v>81.75</v>
       </c>
       <c r="C42">
-        <v>1.0375000000000001</v>
+        <v>1.3625</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>5533</v>
+        <v>4801</v>
       </c>
       <c r="B43">
-        <v>92.216666666666669</v>
+        <v>80.016666666666666</v>
       </c>
       <c r="C43">
-        <v>1.5369444444444444</v>
+        <v>1.3336111111111111</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>10244</v>
+        <v>11579</v>
       </c>
       <c r="B44">
-        <v>170.73333333333332</v>
+        <v>192.98333333333332</v>
       </c>
       <c r="C44">
-        <v>2.8455555555555554</v>
+        <v>3.216388888888889</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>4378</v>
+        <v>3534</v>
       </c>
       <c r="B45">
-        <v>72.966666666666669</v>
+        <v>58.9</v>
       </c>
       <c r="C45">
-        <v>1.2161111111111111</v>
+        <v>0.98166666666666669</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>4118</v>
+        <v>5556</v>
       </c>
       <c r="B46">
-        <v>68.63333333333334</v>
+        <v>92.6</v>
       </c>
       <c r="C46">
-        <v>1.143888888888889</v>
+        <v>1.5433333333333332</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>2042</v>
+        <v>1656</v>
       </c>
       <c r="B47">
-        <v>34.033333333333331</v>
+        <v>27.6</v>
       </c>
       <c r="C47">
-        <v>0.56722222222222218</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>5618</v>
+        <v>2437</v>
       </c>
       <c r="B48">
-        <v>93.63333333333334</v>
+        <v>40.616666666666667</v>
       </c>
       <c r="C48">
-        <v>1.5605555555555555</v>
+        <v>0.67694444444444446</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>13135</v>
+        <v>3508</v>
       </c>
       <c r="B49">
-        <v>218.91666666666666</v>
+        <v>58.466666666666669</v>
       </c>
       <c r="C49">
-        <v>3.6486111111111112</v>
+        <v>0.97444444444444445</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>4003</v>
+        <v>5261</v>
       </c>
       <c r="B50">
-        <v>66.716666666666669</v>
+        <v>87.683333333333337</v>
       </c>
       <c r="C50">
-        <v>1.1119444444444444</v>
+        <v>1.4613888888888888</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>4159</v>
+        <v>4313</v>
       </c>
       <c r="B51">
-        <v>69.316666666666663</v>
+        <v>71.88333333333334</v>
       </c>
       <c r="C51">
-        <v>1.1552777777777778</v>
+        <v>1.1980555555555557</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>2037</v>
+        <v>3385</v>
       </c>
       <c r="B52">
-        <v>33.950000000000003</v>
+        <v>56.416666666666664</v>
       </c>
       <c r="C52">
-        <v>0.5658333333333333</v>
+        <v>0.94027777777777777</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>12801</v>
+        <v>14358</v>
       </c>
       <c r="B53">
-        <v>213.35</v>
+        <v>239.3</v>
       </c>
       <c r="C53">
-        <v>3.5558333333333332</v>
+        <v>3.9883333333333333</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>5698</v>
+        <v>2774</v>
       </c>
       <c r="B54">
-        <v>94.966666666666669</v>
+        <v>46.233333333333334</v>
       </c>
       <c r="C54">
-        <v>1.5827777777777778</v>
+        <v>0.77055555555555555</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>8958</v>
+        <v>5513</v>
       </c>
       <c r="B55">
-        <v>149.30000000000001</v>
+        <v>91.88333333333334</v>
       </c>
       <c r="C55">
-        <v>2.4883333333333333</v>
+        <v>1.5313888888888889</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>5455</v>
+        <v>7544</v>
       </c>
       <c r="B56">
-        <v>90.916666666666671</v>
+        <v>125.73333333333333</v>
       </c>
       <c r="C56">
-        <v>1.5152777777777777</v>
+        <v>2.0955555555555554</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>3134</v>
+        <v>6358</v>
       </c>
       <c r="B57">
-        <v>52.233333333333334</v>
+        <v>105.96666666666667</v>
       </c>
       <c r="C57">
-        <v>0.87055555555555553</v>
+        <v>1.7661111111111112</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>5022</v>
+        <v>5577</v>
       </c>
       <c r="B58">
-        <v>83.7</v>
+        <v>92.95</v>
       </c>
       <c r="C58">
-        <v>1.395</v>
+        <v>1.5491666666666666</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>10345</v>
+        <v>4918</v>
       </c>
       <c r="B59">
-        <v>172.41666666666666</v>
+        <v>81.966666666666669</v>
       </c>
       <c r="C59">
-        <v>2.8736111111111109</v>
+        <v>1.3661111111111111</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>4880</v>
+        <v>5332</v>
       </c>
       <c r="B60">
-        <v>81.333333333333329</v>
+        <v>88.86666666666666</v>
       </c>
       <c r="C60">
-        <v>1.3555555555555556</v>
+        <v>1.481111111111111</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>9557</v>
+        <v>3637</v>
       </c>
       <c r="B61">
-        <v>159.28333333333333</v>
+        <v>60.616666666666667</v>
       </c>
       <c r="C61">
-        <v>2.6547222222222224</v>
+        <v>1.0102777777777778</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>9578</v>
+        <v>9821</v>
       </c>
       <c r="B62">
-        <v>159.63333333333333</v>
+        <v>163.68333333333334</v>
       </c>
       <c r="C62">
-        <v>2.6605555555555553</v>
+        <v>2.7280555555555557</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>3413</v>
+        <v>8146</v>
       </c>
       <c r="B63">
-        <v>56.883333333333333</v>
+        <v>135.76666666666668</v>
       </c>
       <c r="C63">
-        <v>0.94805555555555554</v>
+        <v>2.262777777777778</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>11804</v>
+        <v>5274</v>
       </c>
       <c r="B64">
-        <v>196.73333333333332</v>
+        <v>87.9</v>
       </c>
       <c r="C64">
-        <v>3.278888888888889</v>
+        <v>1.4650000000000001</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>17299</v>
+        <v>2985</v>
       </c>
       <c r="B65">
-        <v>288.31666666666666</v>
+        <v>49.75</v>
       </c>
       <c r="C65">
-        <v>4.8052777777777775</v>
+        <v>0.82916666666666672</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>9940</v>
+        <v>4164</v>
       </c>
       <c r="B66">
-        <v>165.66666666666666</v>
+        <v>69.400000000000006</v>
       </c>
       <c r="C66">
-        <v>2.7611111111111111</v>
+        <v>1.1566666666666667</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>4185</v>
+        <v>7304</v>
       </c>
       <c r="B67">
-        <v>69.75</v>
+        <v>121.73333333333333</v>
       </c>
       <c r="C67">
-        <v>1.1625000000000001</v>
+        <v>2.028888888888889</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>4214</v>
+        <v>4840</v>
       </c>
       <c r="B68">
-        <v>70.233333333333334</v>
+        <v>80.666666666666671</v>
       </c>
       <c r="C68">
-        <v>1.1705555555555556</v>
+        <v>1.3444444444444446</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>4853</v>
+        <v>4460</v>
       </c>
       <c r="B69">
-        <v>80.88333333333334</v>
+        <v>74.333333333333329</v>
       </c>
       <c r="C69">
-        <v>1.3480555555555556</v>
+        <v>1.2388888888888889</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>3857</v>
+        <v>4555</v>
       </c>
       <c r="B70">
-        <v>64.283333333333331</v>
+        <v>75.916666666666671</v>
       </c>
       <c r="C70">
-        <v>1.0713888888888889</v>
+        <v>1.2652777777777777</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>14386</v>
+        <v>3603</v>
       </c>
       <c r="B71">
-        <v>239.76666666666668</v>
+        <v>60.05</v>
       </c>
       <c r="C71">
-        <v>3.9961111111111109</v>
+        <v>1.0008333333333332</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>6377</v>
+        <v>2309</v>
       </c>
       <c r="B72">
-        <v>106.28333333333333</v>
+        <v>38.483333333333334</v>
       </c>
       <c r="C72">
-        <v>1.7713888888888889</v>
+        <v>0.6413888888888889</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>4942</v>
+        <v>5448</v>
       </c>
       <c r="B73">
-        <v>82.36666666666666</v>
+        <v>90.8</v>
       </c>
       <c r="C73">
-        <v>1.3727777777777779</v>
+        <v>1.5133333333333334</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>9667</v>
+        <v>3609</v>
       </c>
       <c r="B74">
-        <v>161.11666666666667</v>
+        <v>60.15</v>
       </c>
       <c r="C74">
-        <v>2.6852777777777779</v>
+        <v>1.0024999999999999</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>2532</v>
+        <v>5556</v>
       </c>
       <c r="B75">
-        <v>42.2</v>
+        <v>92.6</v>
       </c>
       <c r="C75">
-        <v>0.70333333333333337</v>
+        <v>1.5433333333333332</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>4231</v>
+        <v>10096</v>
       </c>
       <c r="B76">
-        <v>70.516666666666666</v>
+        <v>168.26666666666668</v>
       </c>
       <c r="C76">
-        <v>1.1752777777777779</v>
+        <v>2.8044444444444445</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>3207</v>
+        <v>4655</v>
       </c>
       <c r="B77">
-        <v>53.45</v>
+        <v>77.583333333333329</v>
       </c>
       <c r="C77">
-        <v>0.89083333333333337</v>
+        <v>1.2930555555555556</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>6991</v>
+        <v>2318</v>
       </c>
       <c r="B78">
-        <v>116.51666666666667</v>
+        <v>38.633333333333333</v>
       </c>
       <c r="C78">
-        <v>1.9419444444444445</v>
+        <v>0.64388888888888884</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>12951</v>
+        <v>6653</v>
       </c>
       <c r="B79">
-        <v>215.85</v>
+        <v>110.88333333333334</v>
       </c>
       <c r="C79">
-        <v>3.5975000000000001</v>
+        <v>1.8480555555555556</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>5939</v>
+        <v>2652</v>
       </c>
       <c r="B80">
-        <v>98.983333333333334</v>
+        <v>44.2</v>
       </c>
       <c r="C80">
-        <v>1.6497222222222223</v>
+        <v>0.73666666666666669</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>3549</v>
+        <v>15319</v>
       </c>
       <c r="B81">
-        <v>59.15</v>
+        <v>255.31666666666666</v>
       </c>
       <c r="C81">
-        <v>0.98583333333333334</v>
+        <v>4.2552777777777777</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>22178</v>
+        <v>5593</v>
       </c>
       <c r="B82">
-        <v>369.63333333333333</v>
+        <v>93.216666666666669</v>
       </c>
       <c r="C82">
-        <v>6.1605555555555558</v>
+        <v>1.5536111111111111</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>3598</v>
+        <v>6585</v>
       </c>
       <c r="B83">
-        <v>59.966666666666669</v>
+        <v>109.75</v>
       </c>
       <c r="C83">
-        <v>0.99944444444444447</v>
+        <v>1.8291666666666666</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>9764</v>
+        <v>9823</v>
       </c>
       <c r="B84">
-        <v>162.73333333333332</v>
+        <v>163.71666666666667</v>
       </c>
       <c r="C84">
-        <v>2.7122222222222221</v>
+        <v>2.7286111111111113</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>6748</v>
+        <v>3996</v>
       </c>
       <c r="B85">
-        <v>112.46666666666667</v>
+        <v>66.599999999999994</v>
       </c>
       <c r="C85">
-        <v>1.8744444444444444</v>
+        <v>1.1100000000000001</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>6079</v>
+        <v>9721</v>
       </c>
       <c r="B86">
-        <v>101.31666666666666</v>
+        <v>162.01666666666668</v>
       </c>
       <c r="C86">
-        <v>1.6886111111111111</v>
+        <v>2.700277777777778</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>5289</v>
+        <v>7629</v>
       </c>
       <c r="B87">
-        <v>88.15</v>
+        <v>127.15</v>
       </c>
       <c r="C87">
-        <v>1.4691666666666667</v>
+        <v>2.1191666666666666</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>6430</v>
+        <v>2920</v>
       </c>
       <c r="B88">
-        <v>107.16666666666667</v>
+        <v>48.666666666666664</v>
       </c>
       <c r="C88">
-        <v>1.7861111111111112</v>
+        <v>0.81111111111111112</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>10501</v>
+        <v>6460</v>
       </c>
       <c r="B89">
-        <v>175.01666666666668</v>
+        <v>107.66666666666667</v>
       </c>
       <c r="C89">
-        <v>2.9169444444444443</v>
+        <v>1.7944444444444445</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>7554</v>
+        <v>4990</v>
       </c>
       <c r="B90">
-        <v>125.9</v>
+        <v>83.166666666666671</v>
       </c>
       <c r="C90">
-        <v>2.0983333333333332</v>
+        <v>1.3861111111111111</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>10340</v>
+        <v>4696</v>
       </c>
       <c r="B91">
-        <v>172.33333333333334</v>
+        <v>78.266666666666666</v>
       </c>
       <c r="C91">
-        <v>2.8722222222222222</v>
+        <v>1.3044444444444445</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>4578</v>
+        <v>3243</v>
       </c>
       <c r="B92">
-        <v>76.3</v>
+        <v>54.05</v>
       </c>
       <c r="C92">
-        <v>1.2716666666666667</v>
+        <v>0.90083333333333337</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>5188</v>
+        <v>7174</v>
       </c>
       <c r="B93">
-        <v>86.466666666666669</v>
+        <v>119.56666666666666</v>
       </c>
       <c r="C93">
-        <v>1.441111111111111</v>
+        <v>1.9927777777777778</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>4503</v>
+        <v>5224</v>
       </c>
       <c r="B94">
-        <v>75.05</v>
+        <v>87.066666666666663</v>
       </c>
       <c r="C94">
-        <v>1.2508333333333332</v>
+        <v>1.451111111111111</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>5797</v>
+        <v>2147</v>
       </c>
       <c r="B95">
-        <v>96.61666666666666</v>
+        <v>35.783333333333331</v>
       </c>
       <c r="C95">
-        <v>1.6102777777777777</v>
+        <v>0.59638888888888886</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>17511</v>
+        <v>5154</v>
       </c>
       <c r="B96">
-        <v>291.85000000000002</v>
+        <v>85.9</v>
       </c>
       <c r="C96">
-        <v>4.8641666666666667</v>
+        <v>1.4316666666666666</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>1817</v>
+        <v>5334</v>
       </c>
       <c r="B97">
-        <v>30.283333333333335</v>
+        <v>88.9</v>
       </c>
       <c r="C97">
-        <v>0.50472222222222218</v>
+        <v>1.4816666666666667</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>4621</v>
+        <v>3473</v>
       </c>
       <c r="B98">
-        <v>77.016666666666666</v>
+        <v>57.883333333333333</v>
       </c>
       <c r="C98">
-        <v>1.283611111111111</v>
+        <v>0.96472222222222226</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>6064</v>
+        <v>9228</v>
       </c>
       <c r="B99">
-        <v>101.06666666666666</v>
+        <v>153.80000000000001</v>
       </c>
       <c r="C99">
-        <v>1.6844444444444444</v>
+        <v>2.5633333333333335</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>2910</v>
+        <v>4889</v>
       </c>
       <c r="B100">
-        <v>48.5</v>
+        <v>81.483333333333334</v>
       </c>
       <c r="C100">
-        <v>0.80833333333333335</v>
+        <v>1.3580555555555556</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>7520</v>
+        <v>4356</v>
       </c>
       <c r="B101">
-        <v>125.33333333333333</v>
+        <v>72.599999999999994</v>
       </c>
       <c r="C101">
-        <v>2.088888888888889</v>
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Time to Fixation Experiments - Changing Chemotaxis Equation/Experiment 1 - Testing Fixation Time/Time_for_Bac_Fix_Pos50_Start.xlsx
+++ b/Time to Fixation Experiments - Changing Chemotaxis Equation/Experiment 1 - Testing Fixation Time/Time_for_Bac_Fix_Pos50_Start.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\Time to Fixation Experiments - Changing Chemotaxis Equation\Experiment 1 - Testing Fixation Time\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CDF4672-DA27-4F64-A5C1-6001219A8814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F35AFB-28CF-4026-A413-FD14DBD17ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C5D5DF43-D68A-448F-BEE9-BC751A2734F3}"/>
   </bookViews>
@@ -440,6 +440,12 @@
       <c r="B2">
         <v>3396</v>
       </c>
+      <c r="C2">
+        <v>4878</v>
+      </c>
+      <c r="D2">
+        <v>9325</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -448,6 +454,12 @@
       <c r="B3">
         <v>6099</v>
       </c>
+      <c r="C3">
+        <v>4917</v>
+      </c>
+      <c r="D3">
+        <v>7508</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
@@ -456,6 +468,12 @@
       <c r="B4">
         <v>3482</v>
       </c>
+      <c r="C4">
+        <v>2355</v>
+      </c>
+      <c r="D4">
+        <v>3453</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -464,6 +482,12 @@
       <c r="B5">
         <v>4762</v>
       </c>
+      <c r="C5">
+        <v>3168</v>
+      </c>
+      <c r="D5">
+        <v>3480</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -472,6 +496,12 @@
       <c r="B6">
         <v>4366</v>
       </c>
+      <c r="C6">
+        <v>2845</v>
+      </c>
+      <c r="D6">
+        <v>3649</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -480,6 +510,12 @@
       <c r="B7">
         <v>5558</v>
       </c>
+      <c r="C7">
+        <v>9348</v>
+      </c>
+      <c r="D7">
+        <v>6902</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
@@ -488,6 +524,12 @@
       <c r="B8">
         <v>3240</v>
       </c>
+      <c r="C8">
+        <v>4033</v>
+      </c>
+      <c r="D8">
+        <v>4689</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
@@ -496,6 +538,12 @@
       <c r="B9">
         <v>4127</v>
       </c>
+      <c r="C9">
+        <v>3511</v>
+      </c>
+      <c r="D9">
+        <v>3570</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
@@ -504,6 +552,12 @@
       <c r="B10">
         <v>4162</v>
       </c>
+      <c r="C10">
+        <v>3051</v>
+      </c>
+      <c r="D10">
+        <v>4343</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
@@ -512,6 +566,12 @@
       <c r="B11">
         <v>4479</v>
       </c>
+      <c r="C11">
+        <v>6496</v>
+      </c>
+      <c r="D11">
+        <v>7096</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
@@ -520,6 +580,12 @@
       <c r="B12">
         <v>5818</v>
       </c>
+      <c r="C12">
+        <v>3323</v>
+      </c>
+      <c r="D12">
+        <v>4974</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
@@ -528,6 +594,12 @@
       <c r="B13">
         <v>7763</v>
       </c>
+      <c r="C13">
+        <v>4467</v>
+      </c>
+      <c r="D13">
+        <v>6497</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
@@ -536,6 +608,12 @@
       <c r="B14">
         <v>6338</v>
       </c>
+      <c r="C14">
+        <v>1922</v>
+      </c>
+      <c r="D14">
+        <v>3064</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
@@ -544,6 +622,12 @@
       <c r="B15">
         <v>6178</v>
       </c>
+      <c r="C15">
+        <v>2369</v>
+      </c>
+      <c r="D15">
+        <v>3479</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
@@ -552,685 +636,1201 @@
       <c r="B16">
         <v>5700</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C16">
+        <v>3236</v>
+      </c>
+      <c r="D16">
+        <v>6799</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>3267</v>
       </c>
       <c r="B17">
         <v>5154</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C17">
+        <v>2459</v>
+      </c>
+      <c r="D17">
+        <v>3771</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>4544</v>
       </c>
       <c r="B18">
         <v>5867</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C18">
+        <v>4300</v>
+      </c>
+      <c r="D18">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>5881</v>
       </c>
       <c r="B19">
         <v>6106</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C19">
+        <v>2675</v>
+      </c>
+      <c r="D19">
+        <v>4370</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2160</v>
       </c>
       <c r="B20">
         <v>2350</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C20">
+        <v>3188</v>
+      </c>
+      <c r="D20">
+        <v>4902</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>8622</v>
       </c>
       <c r="B21">
         <v>6670</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C21">
+        <v>1828</v>
+      </c>
+      <c r="D21">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>6049</v>
       </c>
       <c r="B22">
         <v>6245</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C22">
+        <v>3792</v>
+      </c>
+      <c r="D22">
+        <v>4260</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2186</v>
       </c>
       <c r="B23">
         <v>6914</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C23">
+        <v>3892</v>
+      </c>
+      <c r="D23">
+        <v>6671</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>6236</v>
       </c>
       <c r="B24">
         <v>6727</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C24">
+        <v>3672</v>
+      </c>
+      <c r="D24">
+        <v>5112</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2035</v>
       </c>
       <c r="B25">
         <v>4708</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C25">
+        <v>3252</v>
+      </c>
+      <c r="D25">
+        <v>4297</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>4360</v>
       </c>
       <c r="B26">
         <v>6313</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C26">
+        <v>5012</v>
+      </c>
+      <c r="D26">
+        <v>6984</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>3470</v>
       </c>
       <c r="B27">
         <v>4411</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C27">
+        <v>3301</v>
+      </c>
+      <c r="D27">
+        <v>3434</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>4732</v>
       </c>
       <c r="B28">
         <v>4863</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C28">
+        <v>3015</v>
+      </c>
+      <c r="D28">
+        <v>9535</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2726</v>
       </c>
       <c r="B29">
         <v>2728</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C29">
+        <v>2026</v>
+      </c>
+      <c r="D29">
+        <v>3505</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>4280</v>
       </c>
       <c r="B30">
         <v>4822</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C30">
+        <v>4306</v>
+      </c>
+      <c r="D30">
+        <v>6469</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2723</v>
       </c>
       <c r="B31">
         <v>3494</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C31">
+        <v>2678</v>
+      </c>
+      <c r="D31">
+        <v>3314</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>6551</v>
       </c>
       <c r="B32">
         <v>7230</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C32">
+        <v>3836</v>
+      </c>
+      <c r="D32">
+        <v>5386</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>6015</v>
       </c>
       <c r="B33">
         <v>6262</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C33">
+        <v>4040</v>
+      </c>
+      <c r="D33">
+        <v>6845</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>9707</v>
       </c>
       <c r="B34">
         <v>12163</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C34">
+        <v>4321</v>
+      </c>
+      <c r="D34">
+        <v>5982</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>4402</v>
       </c>
       <c r="B35">
         <v>6460</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C35">
+        <v>3564</v>
+      </c>
+      <c r="D35">
+        <v>4212</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>5667</v>
       </c>
       <c r="B36">
         <v>6116</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C36">
+        <v>2156</v>
+      </c>
+      <c r="D36">
+        <v>4286</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>1747</v>
       </c>
       <c r="B37">
         <v>1919</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C37">
+        <v>4626</v>
+      </c>
+      <c r="D37">
+        <v>8861</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>3447</v>
       </c>
       <c r="B38">
         <v>3862</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C38">
+        <v>3076</v>
+      </c>
+      <c r="D38">
+        <v>3815</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>3903</v>
       </c>
       <c r="B39">
         <v>4247</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C39">
+        <v>2200</v>
+      </c>
+      <c r="D39">
+        <v>2551</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>12265</v>
       </c>
       <c r="B40">
         <v>8876</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C40">
+        <v>1978</v>
+      </c>
+      <c r="D40">
+        <v>2960</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>6677</v>
       </c>
       <c r="B41">
         <v>8042</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C41">
+        <v>4897</v>
+      </c>
+      <c r="D41">
+        <v>8800</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>4105</v>
       </c>
       <c r="B42">
         <v>4905</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C42">
+        <v>3177</v>
+      </c>
+      <c r="D42">
+        <v>4259</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2687</v>
       </c>
       <c r="B43">
         <v>4801</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C43">
+        <v>3970</v>
+      </c>
+      <c r="D43">
+        <v>5191</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>10349</v>
       </c>
       <c r="B44">
         <v>11579</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C44">
+        <v>5877</v>
+      </c>
+      <c r="D44">
+        <v>8252</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>3533</v>
       </c>
       <c r="B45">
         <v>3534</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C45">
+        <v>7084</v>
+      </c>
+      <c r="D45">
+        <v>9820</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>5366</v>
       </c>
       <c r="B46">
         <v>5556</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C46">
+        <v>6721</v>
+      </c>
+      <c r="D46">
+        <v>8256</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>1657</v>
       </c>
       <c r="B47">
         <v>1656</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C47">
+        <v>4777</v>
+      </c>
+      <c r="D47">
+        <v>7016</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2160</v>
       </c>
       <c r="B48">
         <v>2437</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C48">
+        <v>3509</v>
+      </c>
+      <c r="D48">
+        <v>4037</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>3151</v>
       </c>
       <c r="B49">
         <v>3508</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C49">
+        <v>4678</v>
+      </c>
+      <c r="D49">
+        <v>7135</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2632</v>
       </c>
       <c r="B50">
         <v>5261</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C50">
+        <v>3697</v>
+      </c>
+      <c r="D50">
+        <v>4312</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>8063</v>
       </c>
       <c r="B51">
         <v>4313</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C51">
+        <v>3058</v>
+      </c>
+      <c r="D51">
+        <v>3613</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>3230</v>
       </c>
       <c r="B52">
         <v>3385</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C52">
+        <v>2051</v>
+      </c>
+      <c r="D52">
+        <v>3792</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>11772</v>
       </c>
       <c r="B53">
         <v>14358</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C53">
+        <v>3364</v>
+      </c>
+      <c r="D53">
+        <v>3590</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2003</v>
       </c>
       <c r="B54">
         <v>2774</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C54">
+        <v>1914</v>
+      </c>
+      <c r="D54">
+        <v>3048</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2308</v>
       </c>
       <c r="B55">
         <v>5513</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C55">
+        <v>1834</v>
+      </c>
+      <c r="D55">
+        <v>3170</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>6843</v>
       </c>
       <c r="B56">
         <v>7544</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C56">
+        <v>5463</v>
+      </c>
+      <c r="D56">
+        <v>6534</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>5814</v>
       </c>
       <c r="B57">
         <v>6358</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C57">
+        <v>2477</v>
+      </c>
+      <c r="D57">
+        <v>2973</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>3359</v>
       </c>
       <c r="B58">
         <v>5577</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C58">
+        <v>5092</v>
+      </c>
+      <c r="D58">
+        <v>6903</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>4836</v>
       </c>
       <c r="B59">
         <v>4918</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C59">
+        <v>4861</v>
+      </c>
+      <c r="D59">
+        <v>6088</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>4548</v>
       </c>
       <c r="B60">
         <v>5332</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C60">
+        <v>3460</v>
+      </c>
+      <c r="D60">
+        <v>5241</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>3180</v>
       </c>
       <c r="B61">
         <v>3637</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C61">
+        <v>1445</v>
+      </c>
+      <c r="D61">
+        <v>2337</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>9341</v>
       </c>
       <c r="B62">
         <v>9821</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C62">
+        <v>3954</v>
+      </c>
+      <c r="D62">
+        <v>5331</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>11437</v>
       </c>
       <c r="B63">
         <v>8146</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C63">
+        <v>3677</v>
+      </c>
+      <c r="D63">
+        <v>5944</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>5092</v>
       </c>
       <c r="B64">
         <v>5274</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C64">
+        <v>3749</v>
+      </c>
+      <c r="D64">
+        <v>4403</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>2705</v>
       </c>
       <c r="B65">
         <v>2985</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C65">
+        <v>2745</v>
+      </c>
+      <c r="D65">
+        <v>3123</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>3467</v>
       </c>
       <c r="B66">
         <v>4164</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C66">
+        <v>3229</v>
+      </c>
+      <c r="D66">
+        <v>4072</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>4518</v>
       </c>
       <c r="B67">
         <v>7304</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C67">
+        <v>1646</v>
+      </c>
+      <c r="D67">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>4810</v>
       </c>
       <c r="B68">
         <v>4840</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C68">
+        <v>2050</v>
+      </c>
+      <c r="D68">
+        <v>2771</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>8017</v>
       </c>
       <c r="B69">
         <v>4460</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C69">
+        <v>3046</v>
+      </c>
+      <c r="D69">
+        <v>3762</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>3756</v>
       </c>
       <c r="B70">
         <v>4555</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C70">
+        <v>2154</v>
+      </c>
+      <c r="D70">
+        <v>3108</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>2862</v>
       </c>
       <c r="B71">
         <v>3603</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C71">
+        <v>2776</v>
+      </c>
+      <c r="D71">
+        <v>3768</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>2309</v>
       </c>
       <c r="B72">
         <v>2309</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C72">
+        <v>2163</v>
+      </c>
+      <c r="D72">
+        <v>2954</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>2581</v>
       </c>
       <c r="B73">
         <v>5448</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C73">
+        <v>3770</v>
+      </c>
+      <c r="D73">
+        <v>6016</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>3459</v>
       </c>
       <c r="B74">
         <v>3609</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C74">
+        <v>1912</v>
+      </c>
+      <c r="D74">
+        <v>2642</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>5216</v>
       </c>
       <c r="B75">
         <v>5556</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C75">
+        <v>4952</v>
+      </c>
+      <c r="D75">
+        <v>5739</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>6289</v>
       </c>
       <c r="B76">
         <v>10096</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C76">
+        <v>1510</v>
+      </c>
+      <c r="D76">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>4316</v>
       </c>
       <c r="B77">
         <v>4655</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C77">
+        <v>2746</v>
+      </c>
+      <c r="D77">
+        <v>3492</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>2103</v>
       </c>
       <c r="B78">
         <v>2318</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C78">
+        <v>1814</v>
+      </c>
+      <c r="D78">
+        <v>3342</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>4591</v>
       </c>
       <c r="B79">
         <v>6653</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C79">
+        <v>6497</v>
+      </c>
+      <c r="D79">
+        <v>8504</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>2689</v>
       </c>
       <c r="B80">
         <v>2652</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C80">
+        <v>4164</v>
+      </c>
+      <c r="D80">
+        <v>3413</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>4617</v>
       </c>
       <c r="B81">
         <v>15319</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C81">
+        <v>4571</v>
+      </c>
+      <c r="D81">
+        <v>5837</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>6601</v>
       </c>
       <c r="B82">
         <v>5593</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C82">
+        <v>5373</v>
+      </c>
+      <c r="D82">
+        <v>6429</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>4410</v>
       </c>
       <c r="B83">
         <v>6585</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C83">
+        <v>7163</v>
+      </c>
+      <c r="D83">
+        <v>9512</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>7618</v>
       </c>
       <c r="B84">
         <v>9823</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C84">
+        <v>3596</v>
+      </c>
+      <c r="D84">
+        <v>5882</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>4001</v>
       </c>
       <c r="B85">
         <v>3996</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C85">
+        <v>4655</v>
+      </c>
+      <c r="D85">
+        <v>6908</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>4764</v>
       </c>
       <c r="B86">
         <v>9721</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C86">
+        <v>5258</v>
+      </c>
+      <c r="D86">
+        <v>7235</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>6739</v>
       </c>
       <c r="B87">
         <v>7629</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C87">
+        <v>1358</v>
+      </c>
+      <c r="D87">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>2293</v>
       </c>
       <c r="B88">
         <v>2920</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C88">
+        <v>1844</v>
+      </c>
+      <c r="D88">
+        <v>2387</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>5812</v>
       </c>
       <c r="B89">
         <v>6460</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C89">
+        <v>2138</v>
+      </c>
+      <c r="D89">
+        <v>8873</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>3764</v>
       </c>
       <c r="B90">
         <v>4990</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C90">
+        <v>5919</v>
+      </c>
+      <c r="D90">
+        <v>7254</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>4049</v>
       </c>
       <c r="B91">
         <v>4696</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C91">
+        <v>3669</v>
+      </c>
+      <c r="D91">
+        <v>5294</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>3241</v>
       </c>
       <c r="B92">
         <v>3243</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C92">
+        <v>1856</v>
+      </c>
+      <c r="D92">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>8723</v>
       </c>
       <c r="B93">
         <v>7174</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C93">
+        <v>3288</v>
+      </c>
+      <c r="D93">
+        <v>4272</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>5224</v>
       </c>
       <c r="B94">
         <v>5224</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C94">
+        <v>6440</v>
+      </c>
+      <c r="D94">
+        <v>7887</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>1854</v>
       </c>
       <c r="B95">
         <v>2147</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C95">
+        <v>2584</v>
+      </c>
+      <c r="D95">
+        <v>3106</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>3883</v>
       </c>
       <c r="B96">
         <v>5154</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C96">
+        <v>3996</v>
+      </c>
+      <c r="D96">
+        <v>6387</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>5321</v>
       </c>
       <c r="B97">
         <v>5334</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C97">
+        <v>3265</v>
+      </c>
+      <c r="D97">
+        <v>7081</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>1952</v>
       </c>
       <c r="B98">
         <v>3473</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C98">
+        <v>1465</v>
+      </c>
+      <c r="D98">
+        <v>2414</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>5412</v>
       </c>
       <c r="B99">
         <v>9228</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C99">
+        <v>5837</v>
+      </c>
+      <c r="D99">
+        <v>7013</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>4658</v>
       </c>
       <c r="B100">
         <v>4889</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C100">
+        <v>2638</v>
+      </c>
+      <c r="D100">
+        <v>4643</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>3266</v>
       </c>
       <c r="B101">
         <v>4356</v>
+      </c>
+      <c r="C101">
+        <v>3158</v>
+      </c>
+      <c r="D101">
+        <v>5652</v>
       </c>
     </row>
   </sheetData>
@@ -3490,7 +4090,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7B78790-86BB-4A67-A9C4-9289D98D0CB3}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -3508,6 +4108,1106 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>4878</v>
+      </c>
+      <c r="B2">
+        <v>81.3</v>
+      </c>
+      <c r="C2">
+        <v>1.355</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>4917</v>
+      </c>
+      <c r="B3">
+        <v>81.95</v>
+      </c>
+      <c r="C3">
+        <v>1.3658333333333332</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2355</v>
+      </c>
+      <c r="B4">
+        <v>39.25</v>
+      </c>
+      <c r="C4">
+        <v>0.65416666666666667</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3168</v>
+      </c>
+      <c r="B5">
+        <v>52.8</v>
+      </c>
+      <c r="C5">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2845</v>
+      </c>
+      <c r="B6">
+        <v>47.416666666666664</v>
+      </c>
+      <c r="C6">
+        <v>0.79027777777777775</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>9348</v>
+      </c>
+      <c r="B7">
+        <v>155.80000000000001</v>
+      </c>
+      <c r="C7">
+        <v>2.5966666666666667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>4033</v>
+      </c>
+      <c r="B8">
+        <v>67.216666666666669</v>
+      </c>
+      <c r="C8">
+        <v>1.1202777777777777</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>3511</v>
+      </c>
+      <c r="B9">
+        <v>58.516666666666666</v>
+      </c>
+      <c r="C9">
+        <v>0.9752777777777778</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>3051</v>
+      </c>
+      <c r="B10">
+        <v>50.85</v>
+      </c>
+      <c r="C10">
+        <v>0.84750000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>6496</v>
+      </c>
+      <c r="B11">
+        <v>108.26666666666667</v>
+      </c>
+      <c r="C11">
+        <v>1.8044444444444445</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>3323</v>
+      </c>
+      <c r="B12">
+        <v>55.383333333333333</v>
+      </c>
+      <c r="C12">
+        <v>0.92305555555555552</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>4467</v>
+      </c>
+      <c r="B13">
+        <v>74.45</v>
+      </c>
+      <c r="C13">
+        <v>1.2408333333333332</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1922</v>
+      </c>
+      <c r="B14">
+        <v>32.033333333333331</v>
+      </c>
+      <c r="C14">
+        <v>0.53388888888888886</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2369</v>
+      </c>
+      <c r="B15">
+        <v>39.483333333333334</v>
+      </c>
+      <c r="C15">
+        <v>0.6580555555555555</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>3236</v>
+      </c>
+      <c r="B16">
+        <v>53.93333333333333</v>
+      </c>
+      <c r="C16">
+        <v>0.89888888888888885</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2459</v>
+      </c>
+      <c r="B17">
+        <v>40.983333333333334</v>
+      </c>
+      <c r="C17">
+        <v>0.68305555555555553</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>4300</v>
+      </c>
+      <c r="B18">
+        <v>71.666666666666671</v>
+      </c>
+      <c r="C18">
+        <v>1.1944444444444444</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2675</v>
+      </c>
+      <c r="B19">
+        <v>44.583333333333336</v>
+      </c>
+      <c r="C19">
+        <v>0.74305555555555558</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>3188</v>
+      </c>
+      <c r="B20">
+        <v>53.133333333333333</v>
+      </c>
+      <c r="C20">
+        <v>0.88555555555555554</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>1828</v>
+      </c>
+      <c r="B21">
+        <v>30.466666666666665</v>
+      </c>
+      <c r="C21">
+        <v>0.50777777777777777</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>3792</v>
+      </c>
+      <c r="B22">
+        <v>63.2</v>
+      </c>
+      <c r="C22">
+        <v>1.0533333333333332</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>3892</v>
+      </c>
+      <c r="B23">
+        <v>64.86666666666666</v>
+      </c>
+      <c r="C23">
+        <v>1.0811111111111111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>3672</v>
+      </c>
+      <c r="B24">
+        <v>61.2</v>
+      </c>
+      <c r="C24">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>3252</v>
+      </c>
+      <c r="B25">
+        <v>54.2</v>
+      </c>
+      <c r="C25">
+        <v>0.90333333333333332</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>5012</v>
+      </c>
+      <c r="B26">
+        <v>83.533333333333331</v>
+      </c>
+      <c r="C26">
+        <v>1.3922222222222222</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>3301</v>
+      </c>
+      <c r="B27">
+        <v>55.016666666666666</v>
+      </c>
+      <c r="C27">
+        <v>0.91694444444444445</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>3015</v>
+      </c>
+      <c r="B28">
+        <v>50.25</v>
+      </c>
+      <c r="C28">
+        <v>0.83750000000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2026</v>
+      </c>
+      <c r="B29">
+        <v>33.766666666666666</v>
+      </c>
+      <c r="C29">
+        <v>0.56277777777777782</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>4306</v>
+      </c>
+      <c r="B30">
+        <v>71.766666666666666</v>
+      </c>
+      <c r="C30">
+        <v>1.1961111111111111</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2678</v>
+      </c>
+      <c r="B31">
+        <v>44.633333333333333</v>
+      </c>
+      <c r="C31">
+        <v>0.74388888888888893</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>3836</v>
+      </c>
+      <c r="B32">
+        <v>63.93333333333333</v>
+      </c>
+      <c r="C32">
+        <v>1.0655555555555556</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>4040</v>
+      </c>
+      <c r="B33">
+        <v>67.333333333333329</v>
+      </c>
+      <c r="C33">
+        <v>1.1222222222222222</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>4321</v>
+      </c>
+      <c r="B34">
+        <v>72.016666666666666</v>
+      </c>
+      <c r="C34">
+        <v>1.2002777777777778</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>3564</v>
+      </c>
+      <c r="B35">
+        <v>59.4</v>
+      </c>
+      <c r="C35">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>2156</v>
+      </c>
+      <c r="B36">
+        <v>35.93333333333333</v>
+      </c>
+      <c r="C36">
+        <v>0.59888888888888892</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>4626</v>
+      </c>
+      <c r="B37">
+        <v>77.099999999999994</v>
+      </c>
+      <c r="C37">
+        <v>1.2849999999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>3076</v>
+      </c>
+      <c r="B38">
+        <v>51.266666666666666</v>
+      </c>
+      <c r="C38">
+        <v>0.85444444444444445</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>2200</v>
+      </c>
+      <c r="B39">
+        <v>36.666666666666664</v>
+      </c>
+      <c r="C39">
+        <v>0.61111111111111116</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>1978</v>
+      </c>
+      <c r="B40">
+        <v>32.966666666666669</v>
+      </c>
+      <c r="C40">
+        <v>0.5494444444444444</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>4897</v>
+      </c>
+      <c r="B41">
+        <v>81.61666666666666</v>
+      </c>
+      <c r="C41">
+        <v>1.3602777777777777</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>3177</v>
+      </c>
+      <c r="B42">
+        <v>52.95</v>
+      </c>
+      <c r="C42">
+        <v>0.88249999999999995</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>3970</v>
+      </c>
+      <c r="B43">
+        <v>66.166666666666671</v>
+      </c>
+      <c r="C43">
+        <v>1.1027777777777779</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>5877</v>
+      </c>
+      <c r="B44">
+        <v>97.95</v>
+      </c>
+      <c r="C44">
+        <v>1.6325000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>7084</v>
+      </c>
+      <c r="B45">
+        <v>118.06666666666666</v>
+      </c>
+      <c r="C45">
+        <v>1.9677777777777778</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>6721</v>
+      </c>
+      <c r="B46">
+        <v>112.01666666666667</v>
+      </c>
+      <c r="C46">
+        <v>1.8669444444444445</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>4777</v>
+      </c>
+      <c r="B47">
+        <v>79.61666666666666</v>
+      </c>
+      <c r="C47">
+        <v>1.3269444444444445</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>3509</v>
+      </c>
+      <c r="B48">
+        <v>58.483333333333334</v>
+      </c>
+      <c r="C48">
+        <v>0.97472222222222227</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>4678</v>
+      </c>
+      <c r="B49">
+        <v>77.966666666666669</v>
+      </c>
+      <c r="C49">
+        <v>1.2994444444444444</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>3697</v>
+      </c>
+      <c r="B50">
+        <v>61.616666666666667</v>
+      </c>
+      <c r="C50">
+        <v>1.0269444444444444</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>3058</v>
+      </c>
+      <c r="B51">
+        <v>50.966666666666669</v>
+      </c>
+      <c r="C51">
+        <v>0.84944444444444445</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>2051</v>
+      </c>
+      <c r="B52">
+        <v>34.18333333333333</v>
+      </c>
+      <c r="C52">
+        <v>0.56972222222222224</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>3364</v>
+      </c>
+      <c r="B53">
+        <v>56.06666666666667</v>
+      </c>
+      <c r="C53">
+        <v>0.93444444444444441</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>1914</v>
+      </c>
+      <c r="B54">
+        <v>31.9</v>
+      </c>
+      <c r="C54">
+        <v>0.53166666666666662</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>1834</v>
+      </c>
+      <c r="B55">
+        <v>30.566666666666666</v>
+      </c>
+      <c r="C55">
+        <v>0.50944444444444448</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>5463</v>
+      </c>
+      <c r="B56">
+        <v>91.05</v>
+      </c>
+      <c r="C56">
+        <v>1.5175000000000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>2477</v>
+      </c>
+      <c r="B57">
+        <v>41.283333333333331</v>
+      </c>
+      <c r="C57">
+        <v>0.68805555555555553</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>5092</v>
+      </c>
+      <c r="B58">
+        <v>84.86666666666666</v>
+      </c>
+      <c r="C58">
+        <v>1.4144444444444444</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>4861</v>
+      </c>
+      <c r="B59">
+        <v>81.016666666666666</v>
+      </c>
+      <c r="C59">
+        <v>1.3502777777777777</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>3460</v>
+      </c>
+      <c r="B60">
+        <v>57.666666666666664</v>
+      </c>
+      <c r="C60">
+        <v>0.96111111111111114</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>1445</v>
+      </c>
+      <c r="B61">
+        <v>24.083333333333332</v>
+      </c>
+      <c r="C61">
+        <v>0.40138888888888891</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>3954</v>
+      </c>
+      <c r="B62">
+        <v>65.900000000000006</v>
+      </c>
+      <c r="C62">
+        <v>1.0983333333333334</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>3677</v>
+      </c>
+      <c r="B63">
+        <v>61.283333333333331</v>
+      </c>
+      <c r="C63">
+        <v>1.0213888888888889</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>3749</v>
+      </c>
+      <c r="B64">
+        <v>62.483333333333334</v>
+      </c>
+      <c r="C64">
+        <v>1.0413888888888889</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>2745</v>
+      </c>
+      <c r="B65">
+        <v>45.75</v>
+      </c>
+      <c r="C65">
+        <v>0.76249999999999996</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>3229</v>
+      </c>
+      <c r="B66">
+        <v>53.81666666666667</v>
+      </c>
+      <c r="C66">
+        <v>0.89694444444444443</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>1646</v>
+      </c>
+      <c r="B67">
+        <v>27.433333333333334</v>
+      </c>
+      <c r="C67">
+        <v>0.4572222222222222</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>2050</v>
+      </c>
+      <c r="B68">
+        <v>34.166666666666664</v>
+      </c>
+      <c r="C68">
+        <v>0.56944444444444442</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>3046</v>
+      </c>
+      <c r="B69">
+        <v>50.766666666666666</v>
+      </c>
+      <c r="C69">
+        <v>0.84611111111111115</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>2154</v>
+      </c>
+      <c r="B70">
+        <v>35.9</v>
+      </c>
+      <c r="C70">
+        <v>0.59833333333333338</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>2776</v>
+      </c>
+      <c r="B71">
+        <v>46.266666666666666</v>
+      </c>
+      <c r="C71">
+        <v>0.77111111111111108</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>2163</v>
+      </c>
+      <c r="B72">
+        <v>36.049999999999997</v>
+      </c>
+      <c r="C72">
+        <v>0.60083333333333333</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>3770</v>
+      </c>
+      <c r="B73">
+        <v>62.833333333333336</v>
+      </c>
+      <c r="C73">
+        <v>1.0472222222222223</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>1912</v>
+      </c>
+      <c r="B74">
+        <v>31.866666666666667</v>
+      </c>
+      <c r="C74">
+        <v>0.53111111111111109</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>4952</v>
+      </c>
+      <c r="B75">
+        <v>82.533333333333331</v>
+      </c>
+      <c r="C75">
+        <v>1.3755555555555556</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>1510</v>
+      </c>
+      <c r="B76">
+        <v>25.166666666666668</v>
+      </c>
+      <c r="C76">
+        <v>0.41944444444444445</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>2746</v>
+      </c>
+      <c r="B77">
+        <v>45.766666666666666</v>
+      </c>
+      <c r="C77">
+        <v>0.76277777777777778</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>1814</v>
+      </c>
+      <c r="B78">
+        <v>30.233333333333334</v>
+      </c>
+      <c r="C78">
+        <v>0.50388888888888894</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>6497</v>
+      </c>
+      <c r="B79">
+        <v>108.28333333333333</v>
+      </c>
+      <c r="C79">
+        <v>1.8047222222222221</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>4164</v>
+      </c>
+      <c r="B80">
+        <v>69.400000000000006</v>
+      </c>
+      <c r="C80">
+        <v>1.1566666666666667</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>4571</v>
+      </c>
+      <c r="B81">
+        <v>76.183333333333337</v>
+      </c>
+      <c r="C81">
+        <v>1.2697222222222222</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>5373</v>
+      </c>
+      <c r="B82">
+        <v>89.55</v>
+      </c>
+      <c r="C82">
+        <v>1.4924999999999999</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>7163</v>
+      </c>
+      <c r="B83">
+        <v>119.38333333333334</v>
+      </c>
+      <c r="C83">
+        <v>1.9897222222222222</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>3596</v>
+      </c>
+      <c r="B84">
+        <v>59.93333333333333</v>
+      </c>
+      <c r="C84">
+        <v>0.99888888888888894</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>4655</v>
+      </c>
+      <c r="B85">
+        <v>77.583333333333329</v>
+      </c>
+      <c r="C85">
+        <v>1.2930555555555556</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>5258</v>
+      </c>
+      <c r="B86">
+        <v>87.63333333333334</v>
+      </c>
+      <c r="C86">
+        <v>1.4605555555555556</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>1358</v>
+      </c>
+      <c r="B87">
+        <v>22.633333333333333</v>
+      </c>
+      <c r="C87">
+        <v>0.37722222222222224</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>1844</v>
+      </c>
+      <c r="B88">
+        <v>30.733333333333334</v>
+      </c>
+      <c r="C88">
+        <v>0.51222222222222225</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>2138</v>
+      </c>
+      <c r="B89">
+        <v>35.633333333333333</v>
+      </c>
+      <c r="C89">
+        <v>0.59388888888888891</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>5919</v>
+      </c>
+      <c r="B90">
+        <v>98.65</v>
+      </c>
+      <c r="C90">
+        <v>1.6441666666666668</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>3669</v>
+      </c>
+      <c r="B91">
+        <v>61.15</v>
+      </c>
+      <c r="C91">
+        <v>1.0191666666666668</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>1856</v>
+      </c>
+      <c r="B92">
+        <v>30.933333333333334</v>
+      </c>
+      <c r="C92">
+        <v>0.51555555555555554</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>3288</v>
+      </c>
+      <c r="B93">
+        <v>54.8</v>
+      </c>
+      <c r="C93">
+        <v>0.91333333333333333</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>6440</v>
+      </c>
+      <c r="B94">
+        <v>107.33333333333333</v>
+      </c>
+      <c r="C94">
+        <v>1.788888888888889</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>2584</v>
+      </c>
+      <c r="B95">
+        <v>43.06666666666667</v>
+      </c>
+      <c r="C95">
+        <v>0.71777777777777774</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>3996</v>
+      </c>
+      <c r="B96">
+        <v>66.599999999999994</v>
+      </c>
+      <c r="C96">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>3265</v>
+      </c>
+      <c r="B97">
+        <v>54.416666666666664</v>
+      </c>
+      <c r="C97">
+        <v>0.90694444444444444</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>1465</v>
+      </c>
+      <c r="B98">
+        <v>24.416666666666668</v>
+      </c>
+      <c r="C98">
+        <v>0.40694444444444444</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>5837</v>
+      </c>
+      <c r="B99">
+        <v>97.283333333333331</v>
+      </c>
+      <c r="C99">
+        <v>1.621388888888889</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>2638</v>
+      </c>
+      <c r="B100">
+        <v>43.966666666666669</v>
+      </c>
+      <c r="C100">
+        <v>0.73277777777777775</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>3158</v>
+      </c>
+      <c r="B101">
+        <v>52.633333333333333</v>
+      </c>
+      <c r="C101">
+        <v>0.87722222222222224</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3515,7 +5215,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{700FFB42-EFD7-42BC-9D1E-3691939013EC}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -3533,6 +5233,1106 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>9325</v>
+      </c>
+      <c r="B2">
+        <v>155.41666666666666</v>
+      </c>
+      <c r="C2">
+        <v>2.5902777777777777</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>7508</v>
+      </c>
+      <c r="B3">
+        <v>125.13333333333334</v>
+      </c>
+      <c r="C3">
+        <v>2.0855555555555556</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3453</v>
+      </c>
+      <c r="B4">
+        <v>57.55</v>
+      </c>
+      <c r="C4">
+        <v>0.95916666666666661</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3480</v>
+      </c>
+      <c r="B5">
+        <v>58</v>
+      </c>
+      <c r="C5">
+        <v>0.96666666666666667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>3649</v>
+      </c>
+      <c r="B6">
+        <v>60.81666666666667</v>
+      </c>
+      <c r="C6">
+        <v>1.013611111111111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6902</v>
+      </c>
+      <c r="B7">
+        <v>115.03333333333333</v>
+      </c>
+      <c r="C7">
+        <v>1.9172222222222222</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>4689</v>
+      </c>
+      <c r="B8">
+        <v>78.150000000000006</v>
+      </c>
+      <c r="C8">
+        <v>1.3025</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>3570</v>
+      </c>
+      <c r="B9">
+        <v>59.5</v>
+      </c>
+      <c r="C9">
+        <v>0.9916666666666667</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>4343</v>
+      </c>
+      <c r="B10">
+        <v>72.38333333333334</v>
+      </c>
+      <c r="C10">
+        <v>1.206388888888889</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>7096</v>
+      </c>
+      <c r="B11">
+        <v>118.26666666666667</v>
+      </c>
+      <c r="C11">
+        <v>1.971111111111111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>4974</v>
+      </c>
+      <c r="B12">
+        <v>82.9</v>
+      </c>
+      <c r="C12">
+        <v>1.3816666666666666</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>6497</v>
+      </c>
+      <c r="B13">
+        <v>108.28333333333333</v>
+      </c>
+      <c r="C13">
+        <v>1.8047222222222221</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>3064</v>
+      </c>
+      <c r="B14">
+        <v>51.06666666666667</v>
+      </c>
+      <c r="C14">
+        <v>0.85111111111111115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>3479</v>
+      </c>
+      <c r="B15">
+        <v>57.983333333333334</v>
+      </c>
+      <c r="C15">
+        <v>0.96638888888888885</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>6799</v>
+      </c>
+      <c r="B16">
+        <v>113.31666666666666</v>
+      </c>
+      <c r="C16">
+        <v>1.888611111111111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>3771</v>
+      </c>
+      <c r="B17">
+        <v>62.85</v>
+      </c>
+      <c r="C17">
+        <v>1.0475000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>5600</v>
+      </c>
+      <c r="B18">
+        <v>93.333333333333329</v>
+      </c>
+      <c r="C18">
+        <v>1.5555555555555556</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>4370</v>
+      </c>
+      <c r="B19">
+        <v>72.833333333333329</v>
+      </c>
+      <c r="C19">
+        <v>1.2138888888888888</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>4902</v>
+      </c>
+      <c r="B20">
+        <v>81.7</v>
+      </c>
+      <c r="C20">
+        <v>1.3616666666666666</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>1974</v>
+      </c>
+      <c r="B21">
+        <v>32.9</v>
+      </c>
+      <c r="C21">
+        <v>0.54833333333333334</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>4260</v>
+      </c>
+      <c r="B22">
+        <v>71</v>
+      </c>
+      <c r="C22">
+        <v>1.1833333333333333</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>6671</v>
+      </c>
+      <c r="B23">
+        <v>111.18333333333334</v>
+      </c>
+      <c r="C23">
+        <v>1.8530555555555555</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>5112</v>
+      </c>
+      <c r="B24">
+        <v>85.2</v>
+      </c>
+      <c r="C24">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>4297</v>
+      </c>
+      <c r="B25">
+        <v>71.61666666666666</v>
+      </c>
+      <c r="C25">
+        <v>1.1936111111111112</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>6984</v>
+      </c>
+      <c r="B26">
+        <v>116.4</v>
+      </c>
+      <c r="C26">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>3434</v>
+      </c>
+      <c r="B27">
+        <v>57.233333333333334</v>
+      </c>
+      <c r="C27">
+        <v>0.9538888888888889</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>9535</v>
+      </c>
+      <c r="B28">
+        <v>158.91666666666666</v>
+      </c>
+      <c r="C28">
+        <v>2.6486111111111112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>3505</v>
+      </c>
+      <c r="B29">
+        <v>58.416666666666664</v>
+      </c>
+      <c r="C29">
+        <v>0.97361111111111109</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>6469</v>
+      </c>
+      <c r="B30">
+        <v>107.81666666666666</v>
+      </c>
+      <c r="C30">
+        <v>1.7969444444444445</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>3314</v>
+      </c>
+      <c r="B31">
+        <v>55.233333333333334</v>
+      </c>
+      <c r="C31">
+        <v>0.92055555555555557</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>5386</v>
+      </c>
+      <c r="B32">
+        <v>89.766666666666666</v>
+      </c>
+      <c r="C32">
+        <v>1.4961111111111112</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>6845</v>
+      </c>
+      <c r="B33">
+        <v>114.08333333333333</v>
+      </c>
+      <c r="C33">
+        <v>1.9013888888888888</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>5982</v>
+      </c>
+      <c r="B34">
+        <v>99.7</v>
+      </c>
+      <c r="C34">
+        <v>1.6616666666666666</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>4212</v>
+      </c>
+      <c r="B35">
+        <v>70.2</v>
+      </c>
+      <c r="C35">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>4286</v>
+      </c>
+      <c r="B36">
+        <v>71.433333333333337</v>
+      </c>
+      <c r="C36">
+        <v>1.1905555555555556</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>8861</v>
+      </c>
+      <c r="B37">
+        <v>147.68333333333334</v>
+      </c>
+      <c r="C37">
+        <v>2.4613888888888891</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>3815</v>
+      </c>
+      <c r="B38">
+        <v>63.583333333333336</v>
+      </c>
+      <c r="C38">
+        <v>1.0597222222222222</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>2551</v>
+      </c>
+      <c r="B39">
+        <v>42.516666666666666</v>
+      </c>
+      <c r="C39">
+        <v>0.70861111111111108</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>2960</v>
+      </c>
+      <c r="B40">
+        <v>49.333333333333336</v>
+      </c>
+      <c r="C40">
+        <v>0.82222222222222219</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>8800</v>
+      </c>
+      <c r="B41">
+        <v>146.66666666666666</v>
+      </c>
+      <c r="C41">
+        <v>2.4444444444444446</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>4259</v>
+      </c>
+      <c r="B42">
+        <v>70.983333333333334</v>
+      </c>
+      <c r="C42">
+        <v>1.1830555555555555</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>5191</v>
+      </c>
+      <c r="B43">
+        <v>86.516666666666666</v>
+      </c>
+      <c r="C43">
+        <v>1.4419444444444445</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>8252</v>
+      </c>
+      <c r="B44">
+        <v>137.53333333333333</v>
+      </c>
+      <c r="C44">
+        <v>2.2922222222222222</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>9820</v>
+      </c>
+      <c r="B45">
+        <v>163.66666666666666</v>
+      </c>
+      <c r="C45">
+        <v>2.7277777777777779</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>8256</v>
+      </c>
+      <c r="B46">
+        <v>137.6</v>
+      </c>
+      <c r="C46">
+        <v>2.2933333333333334</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>7016</v>
+      </c>
+      <c r="B47">
+        <v>116.93333333333334</v>
+      </c>
+      <c r="C47">
+        <v>1.9488888888888889</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>4037</v>
+      </c>
+      <c r="B48">
+        <v>67.283333333333331</v>
+      </c>
+      <c r="C48">
+        <v>1.121388888888889</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>7135</v>
+      </c>
+      <c r="B49">
+        <v>118.91666666666667</v>
+      </c>
+      <c r="C49">
+        <v>1.9819444444444445</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>4312</v>
+      </c>
+      <c r="B50">
+        <v>71.86666666666666</v>
+      </c>
+      <c r="C50">
+        <v>1.1977777777777778</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>3613</v>
+      </c>
+      <c r="B51">
+        <v>60.216666666666669</v>
+      </c>
+      <c r="C51">
+        <v>1.003611111111111</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>3792</v>
+      </c>
+      <c r="B52">
+        <v>63.2</v>
+      </c>
+      <c r="C52">
+        <v>1.0533333333333332</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>3590</v>
+      </c>
+      <c r="B53">
+        <v>59.833333333333336</v>
+      </c>
+      <c r="C53">
+        <v>0.99722222222222223</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>3048</v>
+      </c>
+      <c r="B54">
+        <v>50.8</v>
+      </c>
+      <c r="C54">
+        <v>0.84666666666666668</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>3170</v>
+      </c>
+      <c r="B55">
+        <v>52.833333333333336</v>
+      </c>
+      <c r="C55">
+        <v>0.88055555555555554</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>6534</v>
+      </c>
+      <c r="B56">
+        <v>108.9</v>
+      </c>
+      <c r="C56">
+        <v>1.8149999999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>2973</v>
+      </c>
+      <c r="B57">
+        <v>49.55</v>
+      </c>
+      <c r="C57">
+        <v>0.82583333333333331</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>6903</v>
+      </c>
+      <c r="B58">
+        <v>115.05</v>
+      </c>
+      <c r="C58">
+        <v>1.9175</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>6088</v>
+      </c>
+      <c r="B59">
+        <v>101.46666666666667</v>
+      </c>
+      <c r="C59">
+        <v>1.691111111111111</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>5241</v>
+      </c>
+      <c r="B60">
+        <v>87.35</v>
+      </c>
+      <c r="C60">
+        <v>1.4558333333333333</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>2337</v>
+      </c>
+      <c r="B61">
+        <v>38.950000000000003</v>
+      </c>
+      <c r="C61">
+        <v>0.64916666666666667</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>5331</v>
+      </c>
+      <c r="B62">
+        <v>88.85</v>
+      </c>
+      <c r="C62">
+        <v>1.4808333333333332</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>5944</v>
+      </c>
+      <c r="B63">
+        <v>99.066666666666663</v>
+      </c>
+      <c r="C63">
+        <v>1.6511111111111112</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>4403</v>
+      </c>
+      <c r="B64">
+        <v>73.38333333333334</v>
+      </c>
+      <c r="C64">
+        <v>1.2230555555555556</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>3123</v>
+      </c>
+      <c r="B65">
+        <v>52.05</v>
+      </c>
+      <c r="C65">
+        <v>0.86750000000000005</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>4072</v>
+      </c>
+      <c r="B66">
+        <v>67.86666666666666</v>
+      </c>
+      <c r="C66">
+        <v>1.1311111111111112</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>1757</v>
+      </c>
+      <c r="B67">
+        <v>29.283333333333335</v>
+      </c>
+      <c r="C67">
+        <v>0.48805555555555558</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>2771</v>
+      </c>
+      <c r="B68">
+        <v>46.18333333333333</v>
+      </c>
+      <c r="C68">
+        <v>0.7697222222222222</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>3762</v>
+      </c>
+      <c r="B69">
+        <v>62.7</v>
+      </c>
+      <c r="C69">
+        <v>1.0449999999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>3108</v>
+      </c>
+      <c r="B70">
+        <v>51.8</v>
+      </c>
+      <c r="C70">
+        <v>0.86333333333333329</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>3768</v>
+      </c>
+      <c r="B71">
+        <v>62.8</v>
+      </c>
+      <c r="C71">
+        <v>1.0466666666666666</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>2954</v>
+      </c>
+      <c r="B72">
+        <v>49.233333333333334</v>
+      </c>
+      <c r="C72">
+        <v>0.82055555555555559</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>6016</v>
+      </c>
+      <c r="B73">
+        <v>100.26666666666667</v>
+      </c>
+      <c r="C73">
+        <v>1.6711111111111112</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>2642</v>
+      </c>
+      <c r="B74">
+        <v>44.033333333333331</v>
+      </c>
+      <c r="C74">
+        <v>0.73388888888888892</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>5739</v>
+      </c>
+      <c r="B75">
+        <v>95.65</v>
+      </c>
+      <c r="C75">
+        <v>1.5941666666666667</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>1982</v>
+      </c>
+      <c r="B76">
+        <v>33.033333333333331</v>
+      </c>
+      <c r="C76">
+        <v>0.55055555555555558</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>3492</v>
+      </c>
+      <c r="B77">
+        <v>58.2</v>
+      </c>
+      <c r="C77">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>3342</v>
+      </c>
+      <c r="B78">
+        <v>55.7</v>
+      </c>
+      <c r="C78">
+        <v>0.92833333333333334</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>8504</v>
+      </c>
+      <c r="B79">
+        <v>141.73333333333332</v>
+      </c>
+      <c r="C79">
+        <v>2.362222222222222</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>3413</v>
+      </c>
+      <c r="B80">
+        <v>56.883333333333333</v>
+      </c>
+      <c r="C80">
+        <v>0.94805555555555554</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>5837</v>
+      </c>
+      <c r="B81">
+        <v>97.283333333333331</v>
+      </c>
+      <c r="C81">
+        <v>1.621388888888889</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>6429</v>
+      </c>
+      <c r="B82">
+        <v>107.15</v>
+      </c>
+      <c r="C82">
+        <v>1.7858333333333334</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>9512</v>
+      </c>
+      <c r="B83">
+        <v>158.53333333333333</v>
+      </c>
+      <c r="C83">
+        <v>2.6422222222222222</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>5882</v>
+      </c>
+      <c r="B84">
+        <v>98.033333333333331</v>
+      </c>
+      <c r="C84">
+        <v>1.6338888888888889</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>6908</v>
+      </c>
+      <c r="B85">
+        <v>115.13333333333334</v>
+      </c>
+      <c r="C85">
+        <v>1.9188888888888889</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>7235</v>
+      </c>
+      <c r="B86">
+        <v>120.58333333333333</v>
+      </c>
+      <c r="C86">
+        <v>2.0097222222222224</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>1945</v>
+      </c>
+      <c r="B87">
+        <v>32.416666666666664</v>
+      </c>
+      <c r="C87">
+        <v>0.54027777777777775</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>2387</v>
+      </c>
+      <c r="B88">
+        <v>39.783333333333331</v>
+      </c>
+      <c r="C88">
+        <v>0.66305555555555551</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>8873</v>
+      </c>
+      <c r="B89">
+        <v>147.88333333333333</v>
+      </c>
+      <c r="C89">
+        <v>2.464722222222222</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>7254</v>
+      </c>
+      <c r="B90">
+        <v>120.9</v>
+      </c>
+      <c r="C90">
+        <v>2.0150000000000001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>5294</v>
+      </c>
+      <c r="B91">
+        <v>88.233333333333334</v>
+      </c>
+      <c r="C91">
+        <v>1.4705555555555556</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>2069</v>
+      </c>
+      <c r="B92">
+        <v>34.483333333333334</v>
+      </c>
+      <c r="C92">
+        <v>0.57472222222222225</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>4272</v>
+      </c>
+      <c r="B93">
+        <v>71.2</v>
+      </c>
+      <c r="C93">
+        <v>1.1866666666666668</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>7887</v>
+      </c>
+      <c r="B94">
+        <v>131.44999999999999</v>
+      </c>
+      <c r="C94">
+        <v>2.1908333333333334</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>3106</v>
+      </c>
+      <c r="B95">
+        <v>51.766666666666666</v>
+      </c>
+      <c r="C95">
+        <v>0.86277777777777775</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>6387</v>
+      </c>
+      <c r="B96">
+        <v>106.45</v>
+      </c>
+      <c r="C96">
+        <v>1.7741666666666667</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>7081</v>
+      </c>
+      <c r="B97">
+        <v>118.01666666666667</v>
+      </c>
+      <c r="C97">
+        <v>1.9669444444444444</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>2414</v>
+      </c>
+      <c r="B98">
+        <v>40.233333333333334</v>
+      </c>
+      <c r="C98">
+        <v>0.67055555555555557</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>7013</v>
+      </c>
+      <c r="B99">
+        <v>116.88333333333334</v>
+      </c>
+      <c r="C99">
+        <v>1.9480555555555557</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>4643</v>
+      </c>
+      <c r="B100">
+        <v>77.38333333333334</v>
+      </c>
+      <c r="C100">
+        <v>1.2897222222222222</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>5652</v>
+      </c>
+      <c r="B101">
+        <v>94.2</v>
+      </c>
+      <c r="C101">
+        <v>1.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Time to Fixation Experiments - Changing Chemotaxis Equation/Experiment 1 - Testing Fixation Time/Time_for_Bac_Fix_Pos50_Start.xlsx
+++ b/Time to Fixation Experiments - Changing Chemotaxis Equation/Experiment 1 - Testing Fixation Time/Time_for_Bac_Fix_Pos50_Start.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\Time to Fixation Experiments - Changing Chemotaxis Equation\Experiment 1 - Testing Fixation Time\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F35AFB-28CF-4026-A413-FD14DBD17ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E989EB-72A7-4461-8F64-9561082C1BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C5D5DF43-D68A-448F-BEE9-BC751A2734F3}"/>
   </bookViews>
@@ -1354,7 +1354,7 @@
         <v>1646</v>
       </c>
       <c r="D67">
-        <v>1757</v>
+        <v>9325</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -1634,7 +1634,7 @@
         <v>1358</v>
       </c>
       <c r="D87">
-        <v>1945</v>
+        <v>7096</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -1788,7 +1788,7 @@
         <v>1465</v>
       </c>
       <c r="D98">
-        <v>2414</v>
+        <v>7508</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -5238,9 +5238,11 @@
         <v>9325</v>
       </c>
       <c r="B2">
+        <f>A2/60</f>
         <v>155.41666666666666</v>
       </c>
       <c r="C2">
+        <f>A2/3600</f>
         <v>2.5902777777777777</v>
       </c>
     </row>
@@ -5249,9 +5251,11 @@
         <v>7508</v>
       </c>
       <c r="B3">
+        <f t="shared" ref="B3:B66" si="0">A3/60</f>
         <v>125.13333333333334</v>
       </c>
       <c r="C3">
+        <f t="shared" ref="C3:C66" si="1">A3/3600</f>
         <v>2.0855555555555556</v>
       </c>
     </row>
@@ -5260,9 +5264,11 @@
         <v>3453</v>
       </c>
       <c r="B4">
+        <f t="shared" si="0"/>
         <v>57.55</v>
       </c>
       <c r="C4">
+        <f t="shared" si="1"/>
         <v>0.95916666666666661</v>
       </c>
     </row>
@@ -5271,9 +5277,11 @@
         <v>3480</v>
       </c>
       <c r="B5">
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="C5">
+        <f t="shared" si="1"/>
         <v>0.96666666666666667</v>
       </c>
     </row>
@@ -5282,9 +5290,11 @@
         <v>3649</v>
       </c>
       <c r="B6">
+        <f t="shared" si="0"/>
         <v>60.81666666666667</v>
       </c>
       <c r="C6">
+        <f t="shared" si="1"/>
         <v>1.013611111111111</v>
       </c>
     </row>
@@ -5293,9 +5303,11 @@
         <v>6902</v>
       </c>
       <c r="B7">
+        <f t="shared" si="0"/>
         <v>115.03333333333333</v>
       </c>
       <c r="C7">
+        <f t="shared" si="1"/>
         <v>1.9172222222222222</v>
       </c>
     </row>
@@ -5304,9 +5316,11 @@
         <v>4689</v>
       </c>
       <c r="B8">
+        <f t="shared" si="0"/>
         <v>78.150000000000006</v>
       </c>
       <c r="C8">
+        <f t="shared" si="1"/>
         <v>1.3025</v>
       </c>
     </row>
@@ -5315,9 +5329,11 @@
         <v>3570</v>
       </c>
       <c r="B9">
+        <f t="shared" si="0"/>
         <v>59.5</v>
       </c>
       <c r="C9">
+        <f t="shared" si="1"/>
         <v>0.9916666666666667</v>
       </c>
     </row>
@@ -5326,9 +5342,11 @@
         <v>4343</v>
       </c>
       <c r="B10">
+        <f t="shared" si="0"/>
         <v>72.38333333333334</v>
       </c>
       <c r="C10">
+        <f t="shared" si="1"/>
         <v>1.206388888888889</v>
       </c>
     </row>
@@ -5337,9 +5355,11 @@
         <v>7096</v>
       </c>
       <c r="B11">
+        <f t="shared" si="0"/>
         <v>118.26666666666667</v>
       </c>
       <c r="C11">
+        <f t="shared" si="1"/>
         <v>1.971111111111111</v>
       </c>
     </row>
@@ -5348,9 +5368,11 @@
         <v>4974</v>
       </c>
       <c r="B12">
+        <f t="shared" si="0"/>
         <v>82.9</v>
       </c>
       <c r="C12">
+        <f t="shared" si="1"/>
         <v>1.3816666666666666</v>
       </c>
     </row>
@@ -5359,9 +5381,11 @@
         <v>6497</v>
       </c>
       <c r="B13">
+        <f t="shared" si="0"/>
         <v>108.28333333333333</v>
       </c>
       <c r="C13">
+        <f t="shared" si="1"/>
         <v>1.8047222222222221</v>
       </c>
     </row>
@@ -5370,9 +5394,11 @@
         <v>3064</v>
       </c>
       <c r="B14">
+        <f t="shared" si="0"/>
         <v>51.06666666666667</v>
       </c>
       <c r="C14">
+        <f t="shared" si="1"/>
         <v>0.85111111111111115</v>
       </c>
     </row>
@@ -5381,9 +5407,11 @@
         <v>3479</v>
       </c>
       <c r="B15">
+        <f t="shared" si="0"/>
         <v>57.983333333333334</v>
       </c>
       <c r="C15">
+        <f t="shared" si="1"/>
         <v>0.96638888888888885</v>
       </c>
     </row>
@@ -5392,9 +5420,11 @@
         <v>6799</v>
       </c>
       <c r="B16">
+        <f t="shared" si="0"/>
         <v>113.31666666666666</v>
       </c>
       <c r="C16">
+        <f t="shared" si="1"/>
         <v>1.888611111111111</v>
       </c>
     </row>
@@ -5403,9 +5433,11 @@
         <v>3771</v>
       </c>
       <c r="B17">
+        <f t="shared" si="0"/>
         <v>62.85</v>
       </c>
       <c r="C17">
+        <f t="shared" si="1"/>
         <v>1.0475000000000001</v>
       </c>
     </row>
@@ -5414,9 +5446,11 @@
         <v>5600</v>
       </c>
       <c r="B18">
+        <f t="shared" si="0"/>
         <v>93.333333333333329</v>
       </c>
       <c r="C18">
+        <f t="shared" si="1"/>
         <v>1.5555555555555556</v>
       </c>
     </row>
@@ -5425,9 +5459,11 @@
         <v>4370</v>
       </c>
       <c r="B19">
+        <f t="shared" si="0"/>
         <v>72.833333333333329</v>
       </c>
       <c r="C19">
+        <f t="shared" si="1"/>
         <v>1.2138888888888888</v>
       </c>
     </row>
@@ -5436,9 +5472,11 @@
         <v>4902</v>
       </c>
       <c r="B20">
+        <f t="shared" si="0"/>
         <v>81.7</v>
       </c>
       <c r="C20">
+        <f t="shared" si="1"/>
         <v>1.3616666666666666</v>
       </c>
     </row>
@@ -5447,9 +5485,11 @@
         <v>1974</v>
       </c>
       <c r="B21">
+        <f t="shared" si="0"/>
         <v>32.9</v>
       </c>
       <c r="C21">
+        <f t="shared" si="1"/>
         <v>0.54833333333333334</v>
       </c>
     </row>
@@ -5458,9 +5498,11 @@
         <v>4260</v>
       </c>
       <c r="B22">
+        <f t="shared" si="0"/>
         <v>71</v>
       </c>
       <c r="C22">
+        <f t="shared" si="1"/>
         <v>1.1833333333333333</v>
       </c>
     </row>
@@ -5469,9 +5511,11 @@
         <v>6671</v>
       </c>
       <c r="B23">
+        <f t="shared" si="0"/>
         <v>111.18333333333334</v>
       </c>
       <c r="C23">
+        <f t="shared" si="1"/>
         <v>1.8530555555555555</v>
       </c>
     </row>
@@ -5480,9 +5524,11 @@
         <v>5112</v>
       </c>
       <c r="B24">
+        <f t="shared" si="0"/>
         <v>85.2</v>
       </c>
       <c r="C24">
+        <f t="shared" si="1"/>
         <v>1.42</v>
       </c>
     </row>
@@ -5491,9 +5537,11 @@
         <v>4297</v>
       </c>
       <c r="B25">
+        <f t="shared" si="0"/>
         <v>71.61666666666666</v>
       </c>
       <c r="C25">
+        <f t="shared" si="1"/>
         <v>1.1936111111111112</v>
       </c>
     </row>
@@ -5502,9 +5550,11 @@
         <v>6984</v>
       </c>
       <c r="B26">
+        <f t="shared" si="0"/>
         <v>116.4</v>
       </c>
       <c r="C26">
+        <f t="shared" si="1"/>
         <v>1.94</v>
       </c>
     </row>
@@ -5513,9 +5563,11 @@
         <v>3434</v>
       </c>
       <c r="B27">
+        <f t="shared" si="0"/>
         <v>57.233333333333334</v>
       </c>
       <c r="C27">
+        <f t="shared" si="1"/>
         <v>0.9538888888888889</v>
       </c>
     </row>
@@ -5524,9 +5576,11 @@
         <v>9535</v>
       </c>
       <c r="B28">
+        <f t="shared" si="0"/>
         <v>158.91666666666666</v>
       </c>
       <c r="C28">
+        <f t="shared" si="1"/>
         <v>2.6486111111111112</v>
       </c>
     </row>
@@ -5535,9 +5589,11 @@
         <v>3505</v>
       </c>
       <c r="B29">
+        <f t="shared" si="0"/>
         <v>58.416666666666664</v>
       </c>
       <c r="C29">
+        <f t="shared" si="1"/>
         <v>0.97361111111111109</v>
       </c>
     </row>
@@ -5546,9 +5602,11 @@
         <v>6469</v>
       </c>
       <c r="B30">
+        <f t="shared" si="0"/>
         <v>107.81666666666666</v>
       </c>
       <c r="C30">
+        <f t="shared" si="1"/>
         <v>1.7969444444444445</v>
       </c>
     </row>
@@ -5557,9 +5615,11 @@
         <v>3314</v>
       </c>
       <c r="B31">
+        <f t="shared" si="0"/>
         <v>55.233333333333334</v>
       </c>
       <c r="C31">
+        <f t="shared" si="1"/>
         <v>0.92055555555555557</v>
       </c>
     </row>
@@ -5568,9 +5628,11 @@
         <v>5386</v>
       </c>
       <c r="B32">
+        <f t="shared" si="0"/>
         <v>89.766666666666666</v>
       </c>
       <c r="C32">
+        <f t="shared" si="1"/>
         <v>1.4961111111111112</v>
       </c>
     </row>
@@ -5579,9 +5641,11 @@
         <v>6845</v>
       </c>
       <c r="B33">
+        <f t="shared" si="0"/>
         <v>114.08333333333333</v>
       </c>
       <c r="C33">
+        <f t="shared" si="1"/>
         <v>1.9013888888888888</v>
       </c>
     </row>
@@ -5590,9 +5654,11 @@
         <v>5982</v>
       </c>
       <c r="B34">
+        <f t="shared" si="0"/>
         <v>99.7</v>
       </c>
       <c r="C34">
+        <f t="shared" si="1"/>
         <v>1.6616666666666666</v>
       </c>
     </row>
@@ -5601,9 +5667,11 @@
         <v>4212</v>
       </c>
       <c r="B35">
+        <f t="shared" si="0"/>
         <v>70.2</v>
       </c>
       <c r="C35">
+        <f t="shared" si="1"/>
         <v>1.17</v>
       </c>
     </row>
@@ -5612,9 +5680,11 @@
         <v>4286</v>
       </c>
       <c r="B36">
+        <f t="shared" si="0"/>
         <v>71.433333333333337</v>
       </c>
       <c r="C36">
+        <f t="shared" si="1"/>
         <v>1.1905555555555556</v>
       </c>
     </row>
@@ -5623,9 +5693,11 @@
         <v>8861</v>
       </c>
       <c r="B37">
+        <f t="shared" si="0"/>
         <v>147.68333333333334</v>
       </c>
       <c r="C37">
+        <f t="shared" si="1"/>
         <v>2.4613888888888891</v>
       </c>
     </row>
@@ -5634,9 +5706,11 @@
         <v>3815</v>
       </c>
       <c r="B38">
+        <f t="shared" si="0"/>
         <v>63.583333333333336</v>
       </c>
       <c r="C38">
+        <f t="shared" si="1"/>
         <v>1.0597222222222222</v>
       </c>
     </row>
@@ -5645,9 +5719,11 @@
         <v>2551</v>
       </c>
       <c r="B39">
+        <f t="shared" si="0"/>
         <v>42.516666666666666</v>
       </c>
       <c r="C39">
+        <f t="shared" si="1"/>
         <v>0.70861111111111108</v>
       </c>
     </row>
@@ -5656,9 +5732,11 @@
         <v>2960</v>
       </c>
       <c r="B40">
+        <f t="shared" si="0"/>
         <v>49.333333333333336</v>
       </c>
       <c r="C40">
+        <f t="shared" si="1"/>
         <v>0.82222222222222219</v>
       </c>
     </row>
@@ -5667,9 +5745,11 @@
         <v>8800</v>
       </c>
       <c r="B41">
+        <f t="shared" si="0"/>
         <v>146.66666666666666</v>
       </c>
       <c r="C41">
+        <f t="shared" si="1"/>
         <v>2.4444444444444446</v>
       </c>
     </row>
@@ -5678,9 +5758,11 @@
         <v>4259</v>
       </c>
       <c r="B42">
+        <f t="shared" si="0"/>
         <v>70.983333333333334</v>
       </c>
       <c r="C42">
+        <f t="shared" si="1"/>
         <v>1.1830555555555555</v>
       </c>
     </row>
@@ -5689,9 +5771,11 @@
         <v>5191</v>
       </c>
       <c r="B43">
+        <f t="shared" si="0"/>
         <v>86.516666666666666</v>
       </c>
       <c r="C43">
+        <f t="shared" si="1"/>
         <v>1.4419444444444445</v>
       </c>
     </row>
@@ -5700,9 +5784,11 @@
         <v>8252</v>
       </c>
       <c r="B44">
+        <f t="shared" si="0"/>
         <v>137.53333333333333</v>
       </c>
       <c r="C44">
+        <f t="shared" si="1"/>
         <v>2.2922222222222222</v>
       </c>
     </row>
@@ -5711,9 +5797,11 @@
         <v>9820</v>
       </c>
       <c r="B45">
+        <f t="shared" si="0"/>
         <v>163.66666666666666</v>
       </c>
       <c r="C45">
+        <f t="shared" si="1"/>
         <v>2.7277777777777779</v>
       </c>
     </row>
@@ -5722,9 +5810,11 @@
         <v>8256</v>
       </c>
       <c r="B46">
+        <f t="shared" si="0"/>
         <v>137.6</v>
       </c>
       <c r="C46">
+        <f t="shared" si="1"/>
         <v>2.2933333333333334</v>
       </c>
     </row>
@@ -5733,9 +5823,11 @@
         <v>7016</v>
       </c>
       <c r="B47">
+        <f t="shared" si="0"/>
         <v>116.93333333333334</v>
       </c>
       <c r="C47">
+        <f t="shared" si="1"/>
         <v>1.9488888888888889</v>
       </c>
     </row>
@@ -5744,9 +5836,11 @@
         <v>4037</v>
       </c>
       <c r="B48">
+        <f t="shared" si="0"/>
         <v>67.283333333333331</v>
       </c>
       <c r="C48">
+        <f t="shared" si="1"/>
         <v>1.121388888888889</v>
       </c>
     </row>
@@ -5755,9 +5849,11 @@
         <v>7135</v>
       </c>
       <c r="B49">
+        <f t="shared" si="0"/>
         <v>118.91666666666667</v>
       </c>
       <c r="C49">
+        <f t="shared" si="1"/>
         <v>1.9819444444444445</v>
       </c>
     </row>
@@ -5766,9 +5862,11 @@
         <v>4312</v>
       </c>
       <c r="B50">
+        <f t="shared" si="0"/>
         <v>71.86666666666666</v>
       </c>
       <c r="C50">
+        <f t="shared" si="1"/>
         <v>1.1977777777777778</v>
       </c>
     </row>
@@ -5777,9 +5875,11 @@
         <v>3613</v>
       </c>
       <c r="B51">
+        <f t="shared" si="0"/>
         <v>60.216666666666669</v>
       </c>
       <c r="C51">
+        <f t="shared" si="1"/>
         <v>1.003611111111111</v>
       </c>
     </row>
@@ -5788,9 +5888,11 @@
         <v>3792</v>
       </c>
       <c r="B52">
+        <f t="shared" si="0"/>
         <v>63.2</v>
       </c>
       <c r="C52">
+        <f t="shared" si="1"/>
         <v>1.0533333333333332</v>
       </c>
     </row>
@@ -5799,9 +5901,11 @@
         <v>3590</v>
       </c>
       <c r="B53">
+        <f t="shared" si="0"/>
         <v>59.833333333333336</v>
       </c>
       <c r="C53">
+        <f t="shared" si="1"/>
         <v>0.99722222222222223</v>
       </c>
     </row>
@@ -5810,9 +5914,11 @@
         <v>3048</v>
       </c>
       <c r="B54">
+        <f t="shared" si="0"/>
         <v>50.8</v>
       </c>
       <c r="C54">
+        <f t="shared" si="1"/>
         <v>0.84666666666666668</v>
       </c>
     </row>
@@ -5821,9 +5927,11 @@
         <v>3170</v>
       </c>
       <c r="B55">
+        <f t="shared" si="0"/>
         <v>52.833333333333336</v>
       </c>
       <c r="C55">
+        <f t="shared" si="1"/>
         <v>0.88055555555555554</v>
       </c>
     </row>
@@ -5832,9 +5940,11 @@
         <v>6534</v>
       </c>
       <c r="B56">
+        <f t="shared" si="0"/>
         <v>108.9</v>
       </c>
       <c r="C56">
+        <f t="shared" si="1"/>
         <v>1.8149999999999999</v>
       </c>
     </row>
@@ -5843,9 +5953,11 @@
         <v>2973</v>
       </c>
       <c r="B57">
+        <f t="shared" si="0"/>
         <v>49.55</v>
       </c>
       <c r="C57">
+        <f t="shared" si="1"/>
         <v>0.82583333333333331</v>
       </c>
     </row>
@@ -5854,9 +5966,11 @@
         <v>6903</v>
       </c>
       <c r="B58">
+        <f t="shared" si="0"/>
         <v>115.05</v>
       </c>
       <c r="C58">
+        <f t="shared" si="1"/>
         <v>1.9175</v>
       </c>
     </row>
@@ -5865,9 +5979,11 @@
         <v>6088</v>
       </c>
       <c r="B59">
+        <f t="shared" si="0"/>
         <v>101.46666666666667</v>
       </c>
       <c r="C59">
+        <f t="shared" si="1"/>
         <v>1.691111111111111</v>
       </c>
     </row>
@@ -5876,9 +5992,11 @@
         <v>5241</v>
       </c>
       <c r="B60">
+        <f t="shared" si="0"/>
         <v>87.35</v>
       </c>
       <c r="C60">
+        <f t="shared" si="1"/>
         <v>1.4558333333333333</v>
       </c>
     </row>
@@ -5887,9 +6005,11 @@
         <v>2337</v>
       </c>
       <c r="B61">
+        <f t="shared" si="0"/>
         <v>38.950000000000003</v>
       </c>
       <c r="C61">
+        <f t="shared" si="1"/>
         <v>0.64916666666666667</v>
       </c>
     </row>
@@ -5898,9 +6018,11 @@
         <v>5331</v>
       </c>
       <c r="B62">
+        <f t="shared" si="0"/>
         <v>88.85</v>
       </c>
       <c r="C62">
+        <f t="shared" si="1"/>
         <v>1.4808333333333332</v>
       </c>
     </row>
@@ -5909,9 +6031,11 @@
         <v>5944</v>
       </c>
       <c r="B63">
+        <f t="shared" si="0"/>
         <v>99.066666666666663</v>
       </c>
       <c r="C63">
+        <f t="shared" si="1"/>
         <v>1.6511111111111112</v>
       </c>
     </row>
@@ -5920,9 +6044,11 @@
         <v>4403</v>
       </c>
       <c r="B64">
+        <f t="shared" si="0"/>
         <v>73.38333333333334</v>
       </c>
       <c r="C64">
+        <f t="shared" si="1"/>
         <v>1.2230555555555556</v>
       </c>
     </row>
@@ -5931,9 +6057,11 @@
         <v>3123</v>
       </c>
       <c r="B65">
+        <f t="shared" si="0"/>
         <v>52.05</v>
       </c>
       <c r="C65">
+        <f t="shared" si="1"/>
         <v>0.86750000000000005</v>
       </c>
     </row>
@@ -5942,21 +6070,25 @@
         <v>4072</v>
       </c>
       <c r="B66">
+        <f t="shared" si="0"/>
         <v>67.86666666666666</v>
       </c>
       <c r="C66">
+        <f t="shared" si="1"/>
         <v>1.1311111111111112</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>1757</v>
+        <v>9325</v>
       </c>
       <c r="B67">
-        <v>29.283333333333335</v>
+        <f t="shared" ref="B67:B101" si="2">A67/60</f>
+        <v>155.41666666666666</v>
       </c>
       <c r="C67">
-        <v>0.48805555555555558</v>
+        <f t="shared" ref="C67:C101" si="3">A67/3600</f>
+        <v>2.5902777777777777</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -5964,9 +6096,11 @@
         <v>2771</v>
       </c>
       <c r="B68">
+        <f t="shared" si="2"/>
         <v>46.18333333333333</v>
       </c>
       <c r="C68">
+        <f t="shared" si="3"/>
         <v>0.7697222222222222</v>
       </c>
     </row>
@@ -5975,9 +6109,11 @@
         <v>3762</v>
       </c>
       <c r="B69">
+        <f t="shared" si="2"/>
         <v>62.7</v>
       </c>
       <c r="C69">
+        <f t="shared" si="3"/>
         <v>1.0449999999999999</v>
       </c>
     </row>
@@ -5986,9 +6122,11 @@
         <v>3108</v>
       </c>
       <c r="B70">
+        <f t="shared" si="2"/>
         <v>51.8</v>
       </c>
       <c r="C70">
+        <f t="shared" si="3"/>
         <v>0.86333333333333329</v>
       </c>
     </row>
@@ -5997,9 +6135,11 @@
         <v>3768</v>
       </c>
       <c r="B71">
+        <f t="shared" si="2"/>
         <v>62.8</v>
       </c>
       <c r="C71">
+        <f t="shared" si="3"/>
         <v>1.0466666666666666</v>
       </c>
     </row>
@@ -6008,9 +6148,11 @@
         <v>2954</v>
       </c>
       <c r="B72">
+        <f t="shared" si="2"/>
         <v>49.233333333333334</v>
       </c>
       <c r="C72">
+        <f t="shared" si="3"/>
         <v>0.82055555555555559</v>
       </c>
     </row>
@@ -6019,9 +6161,11 @@
         <v>6016</v>
       </c>
       <c r="B73">
+        <f t="shared" si="2"/>
         <v>100.26666666666667</v>
       </c>
       <c r="C73">
+        <f t="shared" si="3"/>
         <v>1.6711111111111112</v>
       </c>
     </row>
@@ -6030,9 +6174,11 @@
         <v>2642</v>
       </c>
       <c r="B74">
+        <f t="shared" si="2"/>
         <v>44.033333333333331</v>
       </c>
       <c r="C74">
+        <f t="shared" si="3"/>
         <v>0.73388888888888892</v>
       </c>
     </row>
@@ -6041,9 +6187,11 @@
         <v>5739</v>
       </c>
       <c r="B75">
+        <f t="shared" si="2"/>
         <v>95.65</v>
       </c>
       <c r="C75">
+        <f t="shared" si="3"/>
         <v>1.5941666666666667</v>
       </c>
     </row>
@@ -6052,9 +6200,11 @@
         <v>1982</v>
       </c>
       <c r="B76">
+        <f t="shared" si="2"/>
         <v>33.033333333333331</v>
       </c>
       <c r="C76">
+        <f t="shared" si="3"/>
         <v>0.55055555555555558</v>
       </c>
     </row>
@@ -6063,9 +6213,11 @@
         <v>3492</v>
       </c>
       <c r="B77">
+        <f t="shared" si="2"/>
         <v>58.2</v>
       </c>
       <c r="C77">
+        <f t="shared" si="3"/>
         <v>0.97</v>
       </c>
     </row>
@@ -6074,9 +6226,11 @@
         <v>3342</v>
       </c>
       <c r="B78">
+        <f t="shared" si="2"/>
         <v>55.7</v>
       </c>
       <c r="C78">
+        <f t="shared" si="3"/>
         <v>0.92833333333333334</v>
       </c>
     </row>
@@ -6085,9 +6239,11 @@
         <v>8504</v>
       </c>
       <c r="B79">
+        <f t="shared" si="2"/>
         <v>141.73333333333332</v>
       </c>
       <c r="C79">
+        <f t="shared" si="3"/>
         <v>2.362222222222222</v>
       </c>
     </row>
@@ -6096,9 +6252,11 @@
         <v>3413</v>
       </c>
       <c r="B80">
+        <f t="shared" si="2"/>
         <v>56.883333333333333</v>
       </c>
       <c r="C80">
+        <f t="shared" si="3"/>
         <v>0.94805555555555554</v>
       </c>
     </row>
@@ -6107,9 +6265,11 @@
         <v>5837</v>
       </c>
       <c r="B81">
+        <f t="shared" si="2"/>
         <v>97.283333333333331</v>
       </c>
       <c r="C81">
+        <f t="shared" si="3"/>
         <v>1.621388888888889</v>
       </c>
     </row>
@@ -6118,9 +6278,11 @@
         <v>6429</v>
       </c>
       <c r="B82">
+        <f t="shared" si="2"/>
         <v>107.15</v>
       </c>
       <c r="C82">
+        <f t="shared" si="3"/>
         <v>1.7858333333333334</v>
       </c>
     </row>
@@ -6129,9 +6291,11 @@
         <v>9512</v>
       </c>
       <c r="B83">
+        <f t="shared" si="2"/>
         <v>158.53333333333333</v>
       </c>
       <c r="C83">
+        <f t="shared" si="3"/>
         <v>2.6422222222222222</v>
       </c>
     </row>
@@ -6140,9 +6304,11 @@
         <v>5882</v>
       </c>
       <c r="B84">
+        <f t="shared" si="2"/>
         <v>98.033333333333331</v>
       </c>
       <c r="C84">
+        <f t="shared" si="3"/>
         <v>1.6338888888888889</v>
       </c>
     </row>
@@ -6151,9 +6317,11 @@
         <v>6908</v>
       </c>
       <c r="B85">
+        <f t="shared" si="2"/>
         <v>115.13333333333334</v>
       </c>
       <c r="C85">
+        <f t="shared" si="3"/>
         <v>1.9188888888888889</v>
       </c>
     </row>
@@ -6162,21 +6330,25 @@
         <v>7235</v>
       </c>
       <c r="B86">
+        <f t="shared" si="2"/>
         <v>120.58333333333333</v>
       </c>
       <c r="C86">
+        <f t="shared" si="3"/>
         <v>2.0097222222222224</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>1945</v>
+        <v>7096</v>
       </c>
       <c r="B87">
-        <v>32.416666666666664</v>
+        <f t="shared" si="2"/>
+        <v>118.26666666666667</v>
       </c>
       <c r="C87">
-        <v>0.54027777777777775</v>
+        <f t="shared" si="3"/>
+        <v>1.971111111111111</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -6184,9 +6356,11 @@
         <v>2387</v>
       </c>
       <c r="B88">
+        <f t="shared" si="2"/>
         <v>39.783333333333331</v>
       </c>
       <c r="C88">
+        <f t="shared" si="3"/>
         <v>0.66305555555555551</v>
       </c>
     </row>
@@ -6195,9 +6369,11 @@
         <v>8873</v>
       </c>
       <c r="B89">
+        <f t="shared" si="2"/>
         <v>147.88333333333333</v>
       </c>
       <c r="C89">
+        <f t="shared" si="3"/>
         <v>2.464722222222222</v>
       </c>
     </row>
@@ -6206,9 +6382,11 @@
         <v>7254</v>
       </c>
       <c r="B90">
+        <f t="shared" si="2"/>
         <v>120.9</v>
       </c>
       <c r="C90">
+        <f t="shared" si="3"/>
         <v>2.0150000000000001</v>
       </c>
     </row>
@@ -6217,9 +6395,11 @@
         <v>5294</v>
       </c>
       <c r="B91">
+        <f t="shared" si="2"/>
         <v>88.233333333333334</v>
       </c>
       <c r="C91">
+        <f t="shared" si="3"/>
         <v>1.4705555555555556</v>
       </c>
     </row>
@@ -6228,9 +6408,11 @@
         <v>2069</v>
       </c>
       <c r="B92">
+        <f t="shared" si="2"/>
         <v>34.483333333333334</v>
       </c>
       <c r="C92">
+        <f t="shared" si="3"/>
         <v>0.57472222222222225</v>
       </c>
     </row>
@@ -6239,9 +6421,11 @@
         <v>4272</v>
       </c>
       <c r="B93">
+        <f t="shared" si="2"/>
         <v>71.2</v>
       </c>
       <c r="C93">
+        <f t="shared" si="3"/>
         <v>1.1866666666666668</v>
       </c>
     </row>
@@ -6250,9 +6434,11 @@
         <v>7887</v>
       </c>
       <c r="B94">
+        <f t="shared" si="2"/>
         <v>131.44999999999999</v>
       </c>
       <c r="C94">
+        <f t="shared" si="3"/>
         <v>2.1908333333333334</v>
       </c>
     </row>
@@ -6261,9 +6447,11 @@
         <v>3106</v>
       </c>
       <c r="B95">
+        <f t="shared" si="2"/>
         <v>51.766666666666666</v>
       </c>
       <c r="C95">
+        <f t="shared" si="3"/>
         <v>0.86277777777777775</v>
       </c>
     </row>
@@ -6272,9 +6460,11 @@
         <v>6387</v>
       </c>
       <c r="B96">
+        <f t="shared" si="2"/>
         <v>106.45</v>
       </c>
       <c r="C96">
+        <f t="shared" si="3"/>
         <v>1.7741666666666667</v>
       </c>
     </row>
@@ -6283,21 +6473,25 @@
         <v>7081</v>
       </c>
       <c r="B97">
+        <f t="shared" si="2"/>
         <v>118.01666666666667</v>
       </c>
       <c r="C97">
+        <f t="shared" si="3"/>
         <v>1.9669444444444444</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>2414</v>
+        <v>7508</v>
       </c>
       <c r="B98">
-        <v>40.233333333333334</v>
+        <f t="shared" si="2"/>
+        <v>125.13333333333334</v>
       </c>
       <c r="C98">
-        <v>0.67055555555555557</v>
+        <f t="shared" si="3"/>
+        <v>2.0855555555555556</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -6305,9 +6499,11 @@
         <v>7013</v>
       </c>
       <c r="B99">
+        <f t="shared" si="2"/>
         <v>116.88333333333334</v>
       </c>
       <c r="C99">
+        <f t="shared" si="3"/>
         <v>1.9480555555555557</v>
       </c>
     </row>
@@ -6316,9 +6512,11 @@
         <v>4643</v>
       </c>
       <c r="B100">
+        <f t="shared" si="2"/>
         <v>77.38333333333334</v>
       </c>
       <c r="C100">
+        <f t="shared" si="3"/>
         <v>1.2897222222222222</v>
       </c>
     </row>
@@ -6327,9 +6525,11 @@
         <v>5652</v>
       </c>
       <c r="B101">
+        <f t="shared" si="2"/>
         <v>94.2</v>
       </c>
       <c r="C101">
+        <f t="shared" si="3"/>
         <v>1.57</v>
       </c>
     </row>
